--- a/data/T3_follower_raw.xlsx
+++ b/data/T3_follower_raw.xlsx
@@ -1959,7 +1959,7 @@
         <v>3</v>
       </c>
       <c r="R2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S2">
         <v>3</v>
@@ -1968,10 +1968,10 @@
         <v>3</v>
       </c>
       <c r="U2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W2">
         <v>6</v>
@@ -2009,7 +2009,7 @@
         <v>4</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
         <v>6</v>
@@ -2042,16 +2042,16 @@
         <v>5</v>
       </c>
       <c r="Q3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R3">
         <v>4</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U3">
         <v>5</v>
@@ -2131,10 +2131,10 @@
         <v>4</v>
       </c>
       <c r="R4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4">
         <v>4</v>
@@ -2152,7 +2152,7 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z4">
         <v>4</v>
@@ -2184,7 +2184,7 @@
         <v>3</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -2282,13 +2282,13 @@
         <v>5</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>2</v>
@@ -2321,13 +2321,13 @@
         <v>6</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA6">
         <v>3</v>
@@ -2389,7 +2389,7 @@
         <v>5</v>
       </c>
       <c r="R7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S7">
         <v>6</v>
@@ -2401,7 +2401,7 @@
         <v>4</v>
       </c>
       <c r="V7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -2451,7 +2451,7 @@
         <v>3</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K8">
         <v>5</v>
@@ -2472,10 +2472,10 @@
         <v>5</v>
       </c>
       <c r="Q8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S8">
         <v>4</v>
@@ -2484,16 +2484,16 @@
         <v>4</v>
       </c>
       <c r="U8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W8">
         <v>6</v>
       </c>
       <c r="X8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y8">
         <v>3</v>
@@ -2522,7 +2522,7 @@
         <v>117</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9">
         <v>4</v>
@@ -2558,7 +2558,7 @@
         <v>4</v>
       </c>
       <c r="Q9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R9">
         <v>5</v>
@@ -2617,7 +2617,7 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10">
         <v>4</v>
@@ -2647,37 +2647,37 @@
         <v>6</v>
       </c>
       <c r="R10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S10">
         <v>6</v>
       </c>
       <c r="T10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U10">
         <v>5</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>6</v>
       </c>
       <c r="X10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y10">
         <v>3</v>
       </c>
       <c r="Z10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA10">
         <v>4</v>
       </c>
       <c r="AB10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:28">
@@ -2706,10 +2706,10 @@
         <v>4</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K11">
         <v>4</v>
@@ -2724,16 +2724,16 @@
         <v>4</v>
       </c>
       <c r="O11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P11">
         <v>4</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S11">
         <v>5</v>
@@ -2745,7 +2745,7 @@
         <v>5</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W11">
         <v>6</v>
@@ -2763,7 +2763,7 @@
         <v>4</v>
       </c>
       <c r="AB11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:28">
@@ -2780,10 +2780,10 @@
         <v>120</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G12">
         <v>4</v>
@@ -2795,13 +2795,13 @@
         <v>5</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M12">
         <v>4</v>
@@ -2822,7 +2822,7 @@
         <v>6</v>
       </c>
       <c r="S12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T12">
         <v>6</v>
@@ -2831,25 +2831,25 @@
         <v>5</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>6</v>
       </c>
       <c r="X12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y12">
         <v>4</v>
       </c>
       <c r="Z12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA12">
         <v>4</v>
       </c>
       <c r="AB12">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:28">
@@ -2869,7 +2869,7 @@
         <v>5</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -2878,7 +2878,7 @@
         <v>5</v>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -2896,7 +2896,7 @@
         <v>3</v>
       </c>
       <c r="O13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P13">
         <v>5</v>
@@ -2911,7 +2911,7 @@
         <v>6</v>
       </c>
       <c r="T13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -2929,7 +2929,7 @@
         <v>3</v>
       </c>
       <c r="Z13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA13">
         <v>3</v>
@@ -2988,7 +2988,7 @@
         <v>5</v>
       </c>
       <c r="Q14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R14">
         <v>3</v>
@@ -3012,10 +3012,10 @@
         <v>4</v>
       </c>
       <c r="Y14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA14">
         <v>3</v>
@@ -3038,16 +3038,16 @@
         <v>123</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15">
         <v>5</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I15">
         <v>4</v>
@@ -3074,19 +3074,19 @@
         <v>5</v>
       </c>
       <c r="Q15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V15">
         <v>4</v>
@@ -3098,16 +3098,16 @@
         <v>2</v>
       </c>
       <c r="Y15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA15">
         <v>3</v>
       </c>
       <c r="AB15">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:28">
@@ -3127,7 +3127,7 @@
         <v>4</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16">
         <v>4</v>
@@ -3145,7 +3145,7 @@
         <v>3</v>
       </c>
       <c r="L16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M16">
         <v>3</v>
@@ -3210,10 +3210,10 @@
         <v>125</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17">
         <v>3</v>
@@ -3228,13 +3228,13 @@
         <v>3</v>
       </c>
       <c r="K17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>4</v>
       </c>
       <c r="M17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>4</v>
@@ -3279,7 +3279,7 @@
         <v>3</v>
       </c>
       <c r="AB17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:28">
@@ -3314,7 +3314,7 @@
         <v>6</v>
       </c>
       <c r="K18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L18">
         <v>4</v>
@@ -3338,7 +3338,7 @@
         <v>6</v>
       </c>
       <c r="S18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T18">
         <v>5</v>
@@ -3362,7 +3362,7 @@
         <v>1</v>
       </c>
       <c r="AA18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB18">
         <v>1</v>
@@ -3418,7 +3418,7 @@
         <v>3</v>
       </c>
       <c r="Q19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R19">
         <v>4</v>
@@ -3430,7 +3430,7 @@
         <v>5</v>
       </c>
       <c r="U19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V19">
         <v>4</v>
@@ -3468,7 +3468,7 @@
         <v>128</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F20">
         <v>6</v>
@@ -3483,13 +3483,13 @@
         <v>3</v>
       </c>
       <c r="J20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>5</v>
       </c>
       <c r="L20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -3507,19 +3507,19 @@
         <v>6</v>
       </c>
       <c r="R20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S20">
         <v>6</v>
       </c>
       <c r="T20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U20">
         <v>6</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W20">
         <v>6</v>
@@ -3557,13 +3557,13 @@
         <v>4</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21">
         <v>4</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I21">
         <v>5</v>
@@ -3593,13 +3593,13 @@
         <v>5</v>
       </c>
       <c r="R21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S21">
         <v>3</v>
       </c>
       <c r="T21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>4</v>
@@ -3611,16 +3611,16 @@
         <v>6</v>
       </c>
       <c r="X21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB21">
         <v>3</v>
@@ -3765,13 +3765,13 @@
         <v>4</v>
       </c>
       <c r="R23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S23">
         <v>4</v>
       </c>
       <c r="T23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U23">
         <v>4</v>
@@ -3907,7 +3907,7 @@
         <v>4</v>
       </c>
       <c r="H25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I25">
         <v>4</v>
@@ -3934,16 +3934,16 @@
         <v>3</v>
       </c>
       <c r="Q25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S25">
         <v>2</v>
       </c>
       <c r="T25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U25">
         <v>2</v>
@@ -3955,19 +3955,19 @@
         <v>6</v>
       </c>
       <c r="X25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y25">
         <v>2</v>
       </c>
       <c r="Z25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA25">
         <v>2</v>
       </c>
       <c r="AB25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:28">
@@ -4020,22 +4020,22 @@
         <v>5</v>
       </c>
       <c r="Q26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S26">
         <v>6</v>
       </c>
       <c r="T26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W26">
         <v>6</v>
@@ -4073,7 +4073,7 @@
         <v>4</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -4109,7 +4109,7 @@
         <v>4</v>
       </c>
       <c r="R27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S27">
         <v>5</v>
@@ -4162,7 +4162,7 @@
         <v>5</v>
       </c>
       <c r="G28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28">
         <v>4</v>
@@ -4198,7 +4198,7 @@
         <v>5</v>
       </c>
       <c r="S28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T28">
         <v>4</v>
@@ -4254,7 +4254,7 @@
         <v>5</v>
       </c>
       <c r="I29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29">
         <v>4</v>
@@ -4272,7 +4272,7 @@
         <v>2</v>
       </c>
       <c r="O29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P29">
         <v>6</v>
@@ -4284,25 +4284,25 @@
         <v>3</v>
       </c>
       <c r="S29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U29">
         <v>3</v>
       </c>
       <c r="V29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W29">
         <v>6</v>
       </c>
       <c r="X29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z29">
         <v>3</v>
@@ -4364,13 +4364,13 @@
         <v>5</v>
       </c>
       <c r="Q30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R30">
         <v>3</v>
       </c>
       <c r="S30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T30">
         <v>3</v>
@@ -4385,7 +4385,7 @@
         <v>6</v>
       </c>
       <c r="X30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y30">
         <v>2</v>
@@ -4456,16 +4456,16 @@
         <v>5</v>
       </c>
       <c r="S31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U31">
         <v>6</v>
       </c>
       <c r="V31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W31">
         <v>6</v>
@@ -4521,7 +4521,7 @@
         <v>6</v>
       </c>
       <c r="L32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M32">
         <v>6</v>
@@ -4672,7 +4672,7 @@
         <v>142</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F34">
         <v>4</v>
@@ -4693,7 +4693,7 @@
         <v>3</v>
       </c>
       <c r="L34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M34">
         <v>3</v>
@@ -4735,13 +4735,13 @@
         <v>3</v>
       </c>
       <c r="Z34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA34">
         <v>2</v>
       </c>
       <c r="AB34">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:28">
@@ -4794,7 +4794,7 @@
         <v>5</v>
       </c>
       <c r="Q35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R35">
         <v>5</v>
@@ -4847,19 +4847,19 @@
         <v>4</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G36">
         <v>4</v>
       </c>
       <c r="H36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I36">
         <v>4</v>
       </c>
       <c r="J36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K36">
         <v>5</v>
@@ -4871,13 +4871,13 @@
         <v>5</v>
       </c>
       <c r="N36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O36">
         <v>4</v>
       </c>
       <c r="P36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q36">
         <v>5</v>
@@ -4936,7 +4936,7 @@
         <v>3</v>
       </c>
       <c r="G37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H37">
         <v>4</v>
@@ -4972,7 +4972,7 @@
         <v>3</v>
       </c>
       <c r="S37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T37">
         <v>4</v>
@@ -4981,7 +4981,7 @@
         <v>4</v>
       </c>
       <c r="V37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W37">
         <v>6</v>
@@ -4990,13 +4990,13 @@
         <v>4</v>
       </c>
       <c r="Y37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z37">
         <v>4</v>
       </c>
       <c r="AA37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB37">
         <v>5</v>
@@ -5028,7 +5028,7 @@
         <v>3</v>
       </c>
       <c r="I38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J38">
         <v>3</v>
@@ -5037,7 +5037,7 @@
         <v>4</v>
       </c>
       <c r="L38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M38">
         <v>4</v>
@@ -5046,7 +5046,7 @@
         <v>4</v>
       </c>
       <c r="O38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P38">
         <v>4</v>
@@ -5055,7 +5055,7 @@
         <v>6</v>
       </c>
       <c r="R38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S38">
         <v>4</v>
@@ -5076,7 +5076,7 @@
         <v>2</v>
       </c>
       <c r="Y38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z38">
         <v>1</v>
@@ -5138,22 +5138,22 @@
         <v>5</v>
       </c>
       <c r="Q39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W39">
         <v>6</v>
@@ -5168,7 +5168,7 @@
         <v>3</v>
       </c>
       <c r="AA39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB39">
         <v>2</v>
@@ -5206,7 +5206,7 @@
         <v>6</v>
       </c>
       <c r="K40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L40">
         <v>4</v>
@@ -5227,7 +5227,7 @@
         <v>7</v>
       </c>
       <c r="R40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S40">
         <v>7</v>
@@ -5251,13 +5251,13 @@
         <v>2</v>
       </c>
       <c r="Z40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA40">
         <v>2</v>
       </c>
       <c r="AB40">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:28">
@@ -5467,7 +5467,7 @@
         <v>4</v>
       </c>
       <c r="L43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M43">
         <v>3</v>
@@ -5509,13 +5509,13 @@
         <v>4</v>
       </c>
       <c r="Z43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB43">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:28">
@@ -5535,7 +5535,7 @@
         <v>6</v>
       </c>
       <c r="F44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G44">
         <v>4</v>
@@ -5577,7 +5577,7 @@
         <v>5</v>
       </c>
       <c r="T44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U44">
         <v>6</v>
@@ -5592,10 +5592,10 @@
         <v>2</v>
       </c>
       <c r="Y44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA44">
         <v>2</v>
@@ -5618,7 +5618,7 @@
         <v>153</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45">
         <v>4</v>
@@ -5633,7 +5633,7 @@
         <v>4</v>
       </c>
       <c r="J45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K45">
         <v>4</v>
@@ -5657,13 +5657,13 @@
         <v>6</v>
       </c>
       <c r="R45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S45">
         <v>6</v>
       </c>
       <c r="T45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U45">
         <v>4</v>
@@ -5684,7 +5684,7 @@
         <v>2</v>
       </c>
       <c r="AA45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB45">
         <v>3</v>
@@ -5725,7 +5725,7 @@
         <v>4</v>
       </c>
       <c r="L46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M46">
         <v>4</v>
@@ -5743,16 +5743,16 @@
         <v>4</v>
       </c>
       <c r="R46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T46">
         <v>4</v>
       </c>
       <c r="U46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V46">
         <v>3</v>
@@ -5761,13 +5761,13 @@
         <v>6</v>
       </c>
       <c r="X46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y46">
         <v>3</v>
       </c>
       <c r="Z46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA46">
         <v>2</v>
@@ -5805,7 +5805,7 @@
         <v>4</v>
       </c>
       <c r="J47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K47">
         <v>5</v>
@@ -5850,7 +5850,7 @@
         <v>2</v>
       </c>
       <c r="Y47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z47">
         <v>2</v>
@@ -5859,7 +5859,7 @@
         <v>2</v>
       </c>
       <c r="AB47">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:28">
@@ -5912,7 +5912,7 @@
         <v>6</v>
       </c>
       <c r="Q48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R48">
         <v>5</v>
@@ -5936,7 +5936,7 @@
         <v>2</v>
       </c>
       <c r="Y48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z48">
         <v>3</v>
@@ -5965,10 +5965,10 @@
         <v>4</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H49">
         <v>3</v>
@@ -5989,16 +5989,16 @@
         <v>4</v>
       </c>
       <c r="N49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O49">
         <v>2</v>
       </c>
       <c r="P49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R49">
         <v>6</v>
@@ -6019,19 +6019,19 @@
         <v>6</v>
       </c>
       <c r="X49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z49">
         <v>2</v>
       </c>
       <c r="AA49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB49">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:28">
@@ -6134,7 +6134,7 @@
         <v>159</v>
       </c>
       <c r="E51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F51">
         <v>4</v>
@@ -6152,7 +6152,7 @@
         <v>4</v>
       </c>
       <c r="K51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L51">
         <v>5</v>
@@ -6200,7 +6200,7 @@
         <v>1</v>
       </c>
       <c r="AA51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB51">
         <v>1</v>
@@ -6259,7 +6259,7 @@
         <v>7</v>
       </c>
       <c r="R52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S52">
         <v>6</v>
@@ -6268,7 +6268,7 @@
         <v>7</v>
       </c>
       <c r="U52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V52">
         <v>6</v>
@@ -6369,10 +6369,10 @@
         <v>4</v>
       </c>
       <c r="Z53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB53">
         <v>4</v>
@@ -6514,7 +6514,7 @@
         <v>3</v>
       </c>
       <c r="Q55">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R55">
         <v>7</v>
@@ -6710,7 +6710,7 @@
         <v>2</v>
       </c>
       <c r="Y57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z57">
         <v>3</v>
@@ -6736,7 +6736,7 @@
         <v>166</v>
       </c>
       <c r="E58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F58">
         <v>4</v>
@@ -6802,7 +6802,7 @@
         <v>4</v>
       </c>
       <c r="AA58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB58">
         <v>3</v>
@@ -6822,7 +6822,7 @@
         <v>167</v>
       </c>
       <c r="E59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F59">
         <v>6</v>
@@ -6953,7 +6953,7 @@
         <v>5</v>
       </c>
       <c r="T60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U60">
         <v>6</v>
@@ -7006,7 +7006,7 @@
         <v>5</v>
       </c>
       <c r="I61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J61">
         <v>5</v>
@@ -7024,7 +7024,7 @@
         <v>2</v>
       </c>
       <c r="O61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P61">
         <v>6</v>
@@ -7036,7 +7036,7 @@
         <v>7</v>
       </c>
       <c r="S61">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T61">
         <v>6</v>
@@ -7060,7 +7060,7 @@
         <v>2</v>
       </c>
       <c r="AA61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB61">
         <v>2</v>
@@ -7119,10 +7119,10 @@
         <v>5</v>
       </c>
       <c r="R62">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S62">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T62">
         <v>5</v>
@@ -7149,7 +7149,7 @@
         <v>3</v>
       </c>
       <c r="AB62">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:28">
@@ -7181,7 +7181,7 @@
         <v>2</v>
       </c>
       <c r="J63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K63">
         <v>5</v>
@@ -7255,7 +7255,7 @@
         <v>3</v>
       </c>
       <c r="F64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G64">
         <v>2</v>
@@ -7270,13 +7270,13 @@
         <v>3</v>
       </c>
       <c r="K64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L64">
         <v>3</v>
       </c>
       <c r="M64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N64">
         <v>5</v>
@@ -7294,7 +7294,7 @@
         <v>4</v>
       </c>
       <c r="S64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T64">
         <v>4</v>
@@ -7303,7 +7303,7 @@
         <v>5</v>
       </c>
       <c r="V64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W64">
         <v>6</v>
@@ -7312,13 +7312,13 @@
         <v>3</v>
       </c>
       <c r="Y64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z64">
         <v>3</v>
       </c>
       <c r="AA64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB64">
         <v>4</v>
@@ -7338,7 +7338,7 @@
         <v>173</v>
       </c>
       <c r="E65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F65">
         <v>5</v>
@@ -7374,7 +7374,7 @@
         <v>5</v>
       </c>
       <c r="Q65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R65">
         <v>5</v>
@@ -7383,13 +7383,13 @@
         <v>4</v>
       </c>
       <c r="T65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U65">
         <v>5</v>
       </c>
       <c r="V65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W65">
         <v>6</v>
@@ -7398,13 +7398,13 @@
         <v>3</v>
       </c>
       <c r="Y65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB65">
         <v>3</v>
@@ -7481,7 +7481,7 @@
         <v>6</v>
       </c>
       <c r="X66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y66">
         <v>5</v>
@@ -7490,7 +7490,7 @@
         <v>4</v>
       </c>
       <c r="AA66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB66">
         <v>5</v>
@@ -7555,10 +7555,10 @@
         <v>4</v>
       </c>
       <c r="T67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V67">
         <v>5</v>
@@ -7694,7 +7694,7 @@
         <v>6</v>
       </c>
       <c r="I69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J69">
         <v>5</v>
@@ -7712,7 +7712,7 @@
         <v>3</v>
       </c>
       <c r="O69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P69">
         <v>5</v>
@@ -7727,7 +7727,7 @@
         <v>7</v>
       </c>
       <c r="T69">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U69">
         <v>7</v>
@@ -7745,13 +7745,13 @@
         <v>2</v>
       </c>
       <c r="Z69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA69">
         <v>2</v>
       </c>
       <c r="AB69">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:28">
@@ -7768,7 +7768,7 @@
         <v>178</v>
       </c>
       <c r="E70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F70">
         <v>5</v>
@@ -7792,7 +7792,7 @@
         <v>5</v>
       </c>
       <c r="M70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N70">
         <v>3</v>
@@ -7816,7 +7816,7 @@
         <v>4</v>
       </c>
       <c r="U70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V70">
         <v>3</v>
@@ -7991,13 +7991,13 @@
         <v>5</v>
       </c>
       <c r="V72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W72">
         <v>6</v>
       </c>
       <c r="X72">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y72">
         <v>4</v>
@@ -8006,7 +8006,7 @@
         <v>3</v>
       </c>
       <c r="AA72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB72">
         <v>5</v>
@@ -8026,7 +8026,7 @@
         <v>181</v>
       </c>
       <c r="E73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F73">
         <v>4</v>
@@ -8047,7 +8047,7 @@
         <v>5</v>
       </c>
       <c r="L73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M73">
         <v>5</v>
@@ -8086,7 +8086,7 @@
         <v>2</v>
       </c>
       <c r="Y73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z73">
         <v>2</v>
@@ -8127,7 +8127,7 @@
         <v>3</v>
       </c>
       <c r="J74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K74">
         <v>4</v>
@@ -8148,22 +8148,22 @@
         <v>4</v>
       </c>
       <c r="Q74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R74">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S74">
         <v>7</v>
       </c>
       <c r="T74">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U74">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W74">
         <v>6</v>
@@ -8175,13 +8175,13 @@
         <v>2</v>
       </c>
       <c r="Z74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA74">
         <v>2</v>
       </c>
       <c r="AB74">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:28">
@@ -8284,13 +8284,13 @@
         <v>184</v>
       </c>
       <c r="E76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F76">
         <v>4</v>
       </c>
       <c r="G76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H76">
         <v>4</v>
@@ -8302,10 +8302,10 @@
         <v>5</v>
       </c>
       <c r="K76">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M76">
         <v>3</v>
@@ -8320,22 +8320,22 @@
         <v>5</v>
       </c>
       <c r="Q76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S76">
         <v>4</v>
       </c>
       <c r="T76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U76">
         <v>3</v>
       </c>
       <c r="V76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W76">
         <v>6</v>
@@ -8344,16 +8344,16 @@
         <v>3</v>
       </c>
       <c r="Y76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB76">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:28">
@@ -8376,7 +8376,7 @@
         <v>5</v>
       </c>
       <c r="G77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H77">
         <v>6</v>
@@ -8436,7 +8436,7 @@
         <v>1</v>
       </c>
       <c r="AA77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB77">
         <v>1</v>
@@ -8542,7 +8542,7 @@
         <v>187</v>
       </c>
       <c r="E79">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F79">
         <v>7</v>
@@ -8551,7 +8551,7 @@
         <v>7</v>
       </c>
       <c r="H79">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I79">
         <v>1</v>
@@ -8634,7 +8634,7 @@
         <v>4</v>
       </c>
       <c r="G80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H80">
         <v>3</v>
@@ -8652,7 +8652,7 @@
         <v>3</v>
       </c>
       <c r="M80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N80">
         <v>3</v>
@@ -8670,10 +8670,10 @@
         <v>3</v>
       </c>
       <c r="S80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U80">
         <v>4</v>
@@ -8685,10 +8685,10 @@
         <v>6</v>
       </c>
       <c r="X80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z80">
         <v>2</v>
@@ -8697,7 +8697,7 @@
         <v>1</v>
       </c>
       <c r="AB80">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:28">
@@ -8726,7 +8726,7 @@
         <v>6</v>
       </c>
       <c r="I81">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J81">
         <v>3</v>
@@ -8744,7 +8744,7 @@
         <v>4</v>
       </c>
       <c r="O81">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P81">
         <v>4</v>
@@ -8836,7 +8836,7 @@
         <v>5</v>
       </c>
       <c r="Q82">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R82">
         <v>5</v>
@@ -8898,7 +8898,7 @@
         <v>5</v>
       </c>
       <c r="I83">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J83">
         <v>5</v>
@@ -8916,7 +8916,7 @@
         <v>4</v>
       </c>
       <c r="O83">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P83">
         <v>4</v>
@@ -8925,7 +8925,7 @@
         <v>5</v>
       </c>
       <c r="R83">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S83">
         <v>5</v>
@@ -8937,13 +8937,13 @@
         <v>4</v>
       </c>
       <c r="V83">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W83">
         <v>6</v>
       </c>
       <c r="X83">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y83">
         <v>4</v>
@@ -9011,7 +9011,7 @@
         <v>6</v>
       </c>
       <c r="R84">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S84">
         <v>6</v>
@@ -9038,7 +9038,7 @@
         <v>2</v>
       </c>
       <c r="AA84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB84">
         <v>1</v>
@@ -9070,7 +9070,7 @@
         <v>4</v>
       </c>
       <c r="I85">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J85">
         <v>5</v>
@@ -9088,7 +9088,7 @@
         <v>3</v>
       </c>
       <c r="O85">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P85">
         <v>5</v>
@@ -9168,7 +9168,7 @@
         <v>5</v>
       </c>
       <c r="M86">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N86">
         <v>3</v>
@@ -9186,13 +9186,13 @@
         <v>6</v>
       </c>
       <c r="S86">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T86">
         <v>4</v>
       </c>
       <c r="U86">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V86">
         <v>5</v>
@@ -9275,7 +9275,7 @@
         <v>4</v>
       </c>
       <c r="T87">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U87">
         <v>4</v>
@@ -9287,7 +9287,7 @@
         <v>6</v>
       </c>
       <c r="X87">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y87">
         <v>4</v>
@@ -9319,7 +9319,7 @@
         <v>4</v>
       </c>
       <c r="F88">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G88">
         <v>4</v>
@@ -9334,10 +9334,10 @@
         <v>4</v>
       </c>
       <c r="K88">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L88">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M88">
         <v>4</v>
@@ -9355,7 +9355,7 @@
         <v>2</v>
       </c>
       <c r="R88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S88">
         <v>2</v>
@@ -9364,7 +9364,7 @@
         <v>3</v>
       </c>
       <c r="U88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V88">
         <v>3</v>
@@ -9382,7 +9382,7 @@
         <v>5</v>
       </c>
       <c r="AA88">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB88">
         <v>4</v>
@@ -9429,13 +9429,13 @@
         <v>6</v>
       </c>
       <c r="N89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O89">
         <v>6</v>
       </c>
       <c r="P89">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q89">
         <v>7</v>
@@ -9488,16 +9488,16 @@
         <v>123</v>
       </c>
       <c r="E90">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F90">
         <v>5</v>
       </c>
       <c r="G90">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H90">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I90">
         <v>4</v>
@@ -9524,19 +9524,19 @@
         <v>5</v>
       </c>
       <c r="Q90">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R90">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S90">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T90">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U90">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V90">
         <v>4</v>
@@ -9548,16 +9548,16 @@
         <v>2</v>
       </c>
       <c r="Y90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA90">
         <v>3</v>
       </c>
       <c r="AB90">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:28">
@@ -9708,10 +9708,10 @@
         <v>3</v>
       </c>
       <c r="U92">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W92">
         <v>6</v>
@@ -9720,16 +9720,16 @@
         <v>4</v>
       </c>
       <c r="Y92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB92">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:28">
@@ -9770,7 +9770,7 @@
         <v>5</v>
       </c>
       <c r="M93">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N93">
         <v>3</v>
@@ -9791,7 +9791,7 @@
         <v>5</v>
       </c>
       <c r="T93">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U93">
         <v>5</v>
@@ -9809,7 +9809,7 @@
         <v>1</v>
       </c>
       <c r="Z93">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA93">
         <v>3</v>
@@ -9841,7 +9841,7 @@
         <v>3</v>
       </c>
       <c r="H94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I94">
         <v>5</v>
@@ -9871,7 +9871,7 @@
         <v>5</v>
       </c>
       <c r="R94">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S94">
         <v>5</v>
@@ -9880,7 +9880,7 @@
         <v>5</v>
       </c>
       <c r="U94">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V94">
         <v>5</v>
@@ -10049,7 +10049,7 @@
         <v>5</v>
       </c>
       <c r="T96">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U96">
         <v>4</v>
@@ -10064,7 +10064,7 @@
         <v>3</v>
       </c>
       <c r="Y96">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z96">
         <v>2</v>
@@ -10093,7 +10093,7 @@
         <v>4</v>
       </c>
       <c r="F97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G97">
         <v>4</v>
@@ -10197,7 +10197,7 @@
         <v>5</v>
       </c>
       <c r="L98">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M98">
         <v>5</v>
@@ -10224,7 +10224,7 @@
         <v>7</v>
       </c>
       <c r="U98">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V98">
         <v>6</v>
@@ -10236,7 +10236,7 @@
         <v>1</v>
       </c>
       <c r="Y98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z98">
         <v>2</v>
@@ -10298,13 +10298,13 @@
         <v>3</v>
       </c>
       <c r="Q99">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R99">
         <v>4</v>
       </c>
       <c r="S99">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T99">
         <v>3</v>
@@ -10319,7 +10319,7 @@
         <v>6</v>
       </c>
       <c r="X99">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y99">
         <v>6</v>
@@ -10331,7 +10331,7 @@
         <v>5</v>
       </c>
       <c r="AB99">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:28">
@@ -10351,7 +10351,7 @@
         <v>4</v>
       </c>
       <c r="F100">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100">
         <v>4</v>
@@ -10360,7 +10360,7 @@
         <v>3</v>
       </c>
       <c r="I100">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J100">
         <v>3</v>
@@ -10378,7 +10378,7 @@
         <v>5</v>
       </c>
       <c r="O100">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P100">
         <v>3</v>
@@ -10399,7 +10399,7 @@
         <v>3</v>
       </c>
       <c r="V100">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W100">
         <v>6</v>
@@ -10414,10 +10414,10 @@
         <v>3</v>
       </c>
       <c r="AA100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB100">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:28">
@@ -10440,10 +10440,10 @@
         <v>5</v>
       </c>
       <c r="G101">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H101">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I101">
         <v>4</v>
@@ -10452,7 +10452,7 @@
         <v>6</v>
       </c>
       <c r="K101">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L101">
         <v>5</v>
@@ -10473,10 +10473,10 @@
         <v>4</v>
       </c>
       <c r="R101">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S101">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T101">
         <v>4</v>
@@ -10497,7 +10497,7 @@
         <v>5</v>
       </c>
       <c r="Z101">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA101">
         <v>4</v>
@@ -10544,7 +10544,7 @@
         <v>6</v>
       </c>
       <c r="M102">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N102">
         <v>1</v>
@@ -10577,10 +10577,10 @@
         <v>6</v>
       </c>
       <c r="X102">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y102">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z102">
         <v>3</v>
@@ -10589,7 +10589,7 @@
         <v>2</v>
       </c>
       <c r="AB102">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103" spans="1:28">
@@ -10651,7 +10651,7 @@
         <v>4</v>
       </c>
       <c r="T103">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U103">
         <v>5</v>
@@ -10663,7 +10663,7 @@
         <v>6</v>
       </c>
       <c r="X103">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y103">
         <v>4</v>
@@ -10692,7 +10692,7 @@
         <v>211</v>
       </c>
       <c r="E104">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F104">
         <v>6</v>
@@ -10713,7 +10713,7 @@
         <v>4</v>
       </c>
       <c r="L104">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M104">
         <v>5</v>
@@ -10731,13 +10731,13 @@
         <v>5</v>
       </c>
       <c r="R104">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S104">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T104">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U104">
         <v>4</v>
@@ -10758,7 +10758,7 @@
         <v>1</v>
       </c>
       <c r="AA104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB104">
         <v>1</v>
@@ -10784,7 +10784,7 @@
         <v>4</v>
       </c>
       <c r="G105">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H105">
         <v>3</v>
@@ -10826,7 +10826,7 @@
         <v>2</v>
       </c>
       <c r="U105">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V105">
         <v>3</v>
@@ -10879,13 +10879,13 @@
         <v>4</v>
       </c>
       <c r="J106">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K106">
         <v>4</v>
       </c>
       <c r="L106">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M106">
         <v>3</v>
@@ -10900,7 +10900,7 @@
         <v>3</v>
       </c>
       <c r="Q106">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R106">
         <v>3</v>
@@ -10915,7 +10915,7 @@
         <v>2</v>
       </c>
       <c r="V106">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W106">
         <v>6</v>
@@ -10933,7 +10933,7 @@
         <v>3</v>
       </c>
       <c r="AB106">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:28">
@@ -11075,16 +11075,16 @@
         <v>3</v>
       </c>
       <c r="R108">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S108">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T108">
         <v>3</v>
       </c>
       <c r="U108">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V108">
         <v>2</v>
@@ -11167,19 +11167,19 @@
         <v>4</v>
       </c>
       <c r="T109">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U109">
         <v>7</v>
       </c>
       <c r="V109">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W109">
         <v>6</v>
       </c>
       <c r="X109">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y109">
         <v>1</v>
@@ -11191,7 +11191,7 @@
         <v>3</v>
       </c>
       <c r="AB109">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:28">
@@ -11244,13 +11244,13 @@
         <v>3</v>
       </c>
       <c r="Q110">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R110">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S110">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T110">
         <v>4</v>
@@ -11265,16 +11265,16 @@
         <v>6</v>
       </c>
       <c r="X110">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y110">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z110">
         <v>4</v>
       </c>
       <c r="AA110">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB110">
         <v>5</v>
@@ -11300,7 +11300,7 @@
         <v>5</v>
       </c>
       <c r="G111">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H111">
         <v>4</v>
@@ -11321,13 +11321,13 @@
         <v>4</v>
       </c>
       <c r="N111">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O111">
         <v>4</v>
       </c>
       <c r="P111">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -11383,7 +11383,7 @@
         <v>4</v>
       </c>
       <c r="F112">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G112">
         <v>5</v>
@@ -11404,22 +11404,22 @@
         <v>4</v>
       </c>
       <c r="M112">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N112">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O112">
         <v>4</v>
       </c>
       <c r="P112">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q112">
         <v>4</v>
       </c>
       <c r="R112">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S112">
         <v>6</v>
@@ -11552,7 +11552,7 @@
         <v>221</v>
       </c>
       <c r="E114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F114">
         <v>3</v>
@@ -11576,7 +11576,7 @@
         <v>4</v>
       </c>
       <c r="M114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N114">
         <v>5</v>
@@ -11638,7 +11638,7 @@
         <v>222</v>
       </c>
       <c r="E115">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F115">
         <v>4</v>
@@ -11653,13 +11653,13 @@
         <v>5</v>
       </c>
       <c r="J115">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K115">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L115">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M115">
         <v>4</v>
@@ -11677,28 +11677,28 @@
         <v>5</v>
       </c>
       <c r="R115">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S115">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T115">
         <v>6</v>
       </c>
       <c r="U115">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V115">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W115">
         <v>6</v>
       </c>
       <c r="X115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y115">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z115">
         <v>3</v>
@@ -11707,7 +11707,7 @@
         <v>2</v>
       </c>
       <c r="AB115">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116" spans="1:28">
@@ -11730,7 +11730,7 @@
         <v>6</v>
       </c>
       <c r="G116">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H116">
         <v>4</v>
@@ -11873,7 +11873,7 @@
         <v>2</v>
       </c>
       <c r="Z117">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA117">
         <v>3</v>
@@ -11902,16 +11902,16 @@
         <v>5</v>
       </c>
       <c r="G118">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H118">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I118">
         <v>2</v>
       </c>
       <c r="J118">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K118">
         <v>5</v>
@@ -11938,16 +11938,16 @@
         <v>4</v>
       </c>
       <c r="S118">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U118">
         <v>4</v>
       </c>
       <c r="V118">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W118">
         <v>6</v>
@@ -11956,16 +11956,16 @@
         <v>4</v>
       </c>
       <c r="Y118">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z118">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA118">
         <v>5</v>
       </c>
       <c r="AB118">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:28">
@@ -11991,7 +11991,7 @@
         <v>4</v>
       </c>
       <c r="H119">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I119">
         <v>5</v>
@@ -12021,7 +12021,7 @@
         <v>5</v>
       </c>
       <c r="R119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S119">
         <v>4</v>
@@ -12068,7 +12068,7 @@
         <v>227</v>
       </c>
       <c r="E120">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F120">
         <v>4</v>
@@ -12178,22 +12178,22 @@
         <v>3</v>
       </c>
       <c r="M121">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N121">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O121">
         <v>4</v>
       </c>
       <c r="P121">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q121">
         <v>2</v>
       </c>
       <c r="R121">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S121">
         <v>4</v>
@@ -12279,10 +12279,10 @@
         <v>4</v>
       </c>
       <c r="R122">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S122">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T122">
         <v>5</v>
@@ -12297,13 +12297,13 @@
         <v>6</v>
       </c>
       <c r="X122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y122">
         <v>1</v>
       </c>
       <c r="Z122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA122">
         <v>2</v>
@@ -12386,7 +12386,7 @@
         <v>1</v>
       </c>
       <c r="Y123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z123">
         <v>3</v>
@@ -12454,7 +12454,7 @@
         <v>5</v>
       </c>
       <c r="S124">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T124">
         <v>5</v>
@@ -12507,7 +12507,7 @@
         <v>4</v>
       </c>
       <c r="H125">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I125">
         <v>4</v>
@@ -12537,10 +12537,10 @@
         <v>2</v>
       </c>
       <c r="R125">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S125">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T125">
         <v>2</v>
@@ -12549,7 +12549,7 @@
         <v>2</v>
       </c>
       <c r="V125">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W125">
         <v>6</v>
@@ -12602,13 +12602,13 @@
         <v>5</v>
       </c>
       <c r="K126">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L126">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M126">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N126">
         <v>3</v>
@@ -12644,7 +12644,7 @@
         <v>4</v>
       </c>
       <c r="Y126">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z126">
         <v>4</v>
@@ -12670,10 +12670,10 @@
         <v>234</v>
       </c>
       <c r="E127">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F127">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G127">
         <v>4</v>
@@ -12682,7 +12682,7 @@
         <v>7</v>
       </c>
       <c r="I127">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J127">
         <v>5</v>
@@ -12700,7 +12700,7 @@
         <v>2</v>
       </c>
       <c r="O127">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P127">
         <v>6</v>
@@ -12733,7 +12733,7 @@
         <v>1</v>
       </c>
       <c r="Z127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA127">
         <v>1</v>
@@ -12762,7 +12762,7 @@
         <v>5</v>
       </c>
       <c r="G128">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H128">
         <v>5</v>
@@ -12881,7 +12881,7 @@
         <v>6</v>
       </c>
       <c r="R129">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S129">
         <v>5</v>
@@ -12967,19 +12967,19 @@
         <v>2</v>
       </c>
       <c r="R130">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S130">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T130">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U130">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V130">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W130">
         <v>6</v>
@@ -13023,7 +13023,7 @@
         <v>5</v>
       </c>
       <c r="H131">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I131">
         <v>2</v>
@@ -13032,10 +13032,10 @@
         <v>6</v>
       </c>
       <c r="K131">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L131">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M131">
         <v>5</v>
@@ -13074,7 +13074,7 @@
         <v>3</v>
       </c>
       <c r="Y131">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z131">
         <v>3</v>
@@ -13139,10 +13139,10 @@
         <v>5</v>
       </c>
       <c r="R132">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S132">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T132">
         <v>5</v>
@@ -13160,16 +13160,16 @@
         <v>1</v>
       </c>
       <c r="Y132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z132">
         <v>1</v>
       </c>
       <c r="AA132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB132">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:28">
@@ -13189,10 +13189,10 @@
         <v>5</v>
       </c>
       <c r="F133">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G133">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H133">
         <v>3</v>
@@ -13243,7 +13243,7 @@
         <v>6</v>
       </c>
       <c r="X133">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y133">
         <v>3</v>
@@ -13252,7 +13252,7 @@
         <v>3</v>
       </c>
       <c r="AA133">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB133">
         <v>4</v>
@@ -13308,37 +13308,37 @@
         <v>3</v>
       </c>
       <c r="Q134">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R134">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S134">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T134">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U134">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V134">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W134">
         <v>6</v>
       </c>
       <c r="X134">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y134">
         <v>3</v>
       </c>
       <c r="Z134">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA134">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB134">
         <v>4</v>
@@ -13364,7 +13364,7 @@
         <v>5</v>
       </c>
       <c r="G135">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H135">
         <v>5</v>
@@ -13382,7 +13382,7 @@
         <v>5</v>
       </c>
       <c r="M135">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N135">
         <v>3</v>
@@ -13394,7 +13394,7 @@
         <v>5</v>
       </c>
       <c r="Q135">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R135">
         <v>6</v>
@@ -13409,7 +13409,7 @@
         <v>6</v>
       </c>
       <c r="V135">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W135">
         <v>6</v>
@@ -13536,7 +13536,7 @@
         <v>5</v>
       </c>
       <c r="G137">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H137">
         <v>5</v>
@@ -13566,7 +13566,7 @@
         <v>4</v>
       </c>
       <c r="Q137">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R137">
         <v>7</v>
@@ -13596,7 +13596,7 @@
         <v>2</v>
       </c>
       <c r="AA137">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB137">
         <v>1</v>
@@ -13619,13 +13619,13 @@
         <v>5</v>
       </c>
       <c r="F138">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G138">
         <v>4</v>
       </c>
       <c r="H138">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I138">
         <v>3</v>
@@ -13640,7 +13640,7 @@
         <v>4</v>
       </c>
       <c r="M138">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N138">
         <v>4</v>
@@ -13676,7 +13676,7 @@
         <v>3</v>
       </c>
       <c r="Y138">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z138">
         <v>2</v>
@@ -13711,7 +13711,7 @@
         <v>5</v>
       </c>
       <c r="H139">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I139">
         <v>3</v>
@@ -13744,13 +13744,13 @@
         <v>6</v>
       </c>
       <c r="S139">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T139">
         <v>5</v>
       </c>
       <c r="U139">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V139">
         <v>6</v>
@@ -13913,7 +13913,7 @@
         <v>3</v>
       </c>
       <c r="R141">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S141">
         <v>4</v>
@@ -13925,25 +13925,25 @@
         <v>4</v>
       </c>
       <c r="V141">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W141">
         <v>6</v>
       </c>
       <c r="X141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y141">
         <v>2</v>
       </c>
       <c r="Z141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA141">
         <v>2</v>
       </c>
       <c r="AB141">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:28">
@@ -13975,7 +13975,7 @@
         <v>3</v>
       </c>
       <c r="J142">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K142">
         <v>5</v>
@@ -14008,7 +14008,7 @@
         <v>5</v>
       </c>
       <c r="U142">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V142">
         <v>4</v>
@@ -14174,7 +14174,7 @@
         <v>4</v>
       </c>
       <c r="S144">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T144">
         <v>4</v>
@@ -14307,7 +14307,7 @@
         <v>4</v>
       </c>
       <c r="F146">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G146">
         <v>4</v>
@@ -14328,7 +14328,7 @@
         <v>5</v>
       </c>
       <c r="M146">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N146">
         <v>3</v>
@@ -14393,13 +14393,13 @@
         <v>6</v>
       </c>
       <c r="F147">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G147">
         <v>5</v>
       </c>
       <c r="H147">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I147">
         <v>3</v>
@@ -14417,28 +14417,28 @@
         <v>5</v>
       </c>
       <c r="N147">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O147">
         <v>5</v>
       </c>
       <c r="P147">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q147">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R147">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S147">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T147">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U147">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V147">
         <v>6</v>
@@ -14447,16 +14447,16 @@
         <v>6</v>
       </c>
       <c r="X147">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y147">
         <v>4</v>
       </c>
       <c r="Z147">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA147">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB147">
         <v>3</v>
@@ -14512,16 +14512,16 @@
         <v>4</v>
       </c>
       <c r="Q148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R148">
         <v>3</v>
       </c>
       <c r="S148">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T148">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U148">
         <v>2</v>
@@ -14542,7 +14542,7 @@
         <v>4</v>
       </c>
       <c r="AA148">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB148">
         <v>4</v>
@@ -14574,7 +14574,7 @@
         <v>5</v>
       </c>
       <c r="I149">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J149">
         <v>5</v>
@@ -14592,7 +14592,7 @@
         <v>2</v>
       </c>
       <c r="O149">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P149">
         <v>6</v>
@@ -14604,10 +14604,10 @@
         <v>6</v>
       </c>
       <c r="S149">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T149">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U149">
         <v>6</v>
@@ -14622,16 +14622,16 @@
         <v>3</v>
       </c>
       <c r="Y149">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z149">
         <v>2</v>
       </c>
       <c r="AA149">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB149">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150" spans="1:28">
@@ -14657,16 +14657,16 @@
         <v>4</v>
       </c>
       <c r="H150">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I150">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J150">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K150">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L150">
         <v>4</v>
@@ -14678,7 +14678,7 @@
         <v>3</v>
       </c>
       <c r="O150">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P150">
         <v>5</v>
@@ -14696,10 +14696,10 @@
         <v>5</v>
       </c>
       <c r="U150">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V150">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W150">
         <v>6</v>
@@ -14708,10 +14708,10 @@
         <v>3</v>
       </c>
       <c r="Y150">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z150">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA150">
         <v>2</v>
@@ -14859,16 +14859,16 @@
         <v>3</v>
       </c>
       <c r="R152">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S152">
         <v>3</v>
       </c>
       <c r="T152">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U152">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V152">
         <v>2</v>
@@ -14877,7 +14877,7 @@
         <v>6</v>
       </c>
       <c r="X152">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y152">
         <v>3</v>
@@ -14909,7 +14909,7 @@
         <v>5</v>
       </c>
       <c r="F153">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G153">
         <v>5</v>
@@ -14924,7 +14924,7 @@
         <v>4</v>
       </c>
       <c r="K153">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L153">
         <v>4</v>
@@ -14945,13 +14945,13 @@
         <v>7</v>
       </c>
       <c r="R153">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S153">
         <v>6</v>
       </c>
       <c r="T153">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U153">
         <v>7</v>
@@ -14972,7 +14972,7 @@
         <v>1</v>
       </c>
       <c r="AA153">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB153">
         <v>2</v>
@@ -14998,7 +14998,7 @@
         <v>5</v>
       </c>
       <c r="G154">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H154">
         <v>5</v>
@@ -15043,7 +15043,7 @@
         <v>4</v>
       </c>
       <c r="V154">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W154">
         <v>6</v>
@@ -15078,7 +15078,7 @@
         <v>262</v>
       </c>
       <c r="E155">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F155">
         <v>4</v>
@@ -15090,7 +15090,7 @@
         <v>5</v>
       </c>
       <c r="I155">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J155">
         <v>4</v>
@@ -15108,7 +15108,7 @@
         <v>3</v>
       </c>
       <c r="O155">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P155">
         <v>5</v>
@@ -15123,7 +15123,7 @@
         <v>3</v>
       </c>
       <c r="T155">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U155">
         <v>4</v>
@@ -15144,7 +15144,7 @@
         <v>3</v>
       </c>
       <c r="AA155">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB155">
         <v>2</v>
@@ -15250,7 +15250,7 @@
         <v>264</v>
       </c>
       <c r="E157">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F157">
         <v>4</v>
@@ -15336,7 +15336,7 @@
         <v>265</v>
       </c>
       <c r="E158">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F158">
         <v>5</v>
@@ -15375,19 +15375,19 @@
         <v>4</v>
       </c>
       <c r="R158">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S158">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T158">
         <v>5</v>
       </c>
       <c r="U158">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V158">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W158">
         <v>6</v>
@@ -15405,7 +15405,7 @@
         <v>3</v>
       </c>
       <c r="AB158">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159" spans="1:28">
@@ -15479,7 +15479,7 @@
         <v>6</v>
       </c>
       <c r="X159">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y159">
         <v>1</v>
@@ -15508,13 +15508,13 @@
         <v>267</v>
       </c>
       <c r="E160">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F160">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G160">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H160">
         <v>5</v>
@@ -15523,7 +15523,7 @@
         <v>3</v>
       </c>
       <c r="J160">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K160">
         <v>6</v>
@@ -15532,7 +15532,7 @@
         <v>4</v>
       </c>
       <c r="M160">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N160">
         <v>3</v>
@@ -15544,10 +15544,10 @@
         <v>5</v>
       </c>
       <c r="Q160">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R160">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S160">
         <v>5</v>
@@ -15568,16 +15568,16 @@
         <v>5</v>
       </c>
       <c r="Y160">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z160">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA160">
         <v>4</v>
       </c>
       <c r="AB160">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161" spans="1:28">
@@ -15645,7 +15645,7 @@
         <v>5</v>
       </c>
       <c r="V161">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W161">
         <v>6</v>
@@ -15660,7 +15660,7 @@
         <v>2</v>
       </c>
       <c r="AA161">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB161">
         <v>3</v>
@@ -15775,13 +15775,13 @@
         <v>3</v>
       </c>
       <c r="H163">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I163">
         <v>5</v>
       </c>
       <c r="J163">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K163">
         <v>3</v>
@@ -15790,7 +15790,7 @@
         <v>3</v>
       </c>
       <c r="M163">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N163">
         <v>5</v>
@@ -15808,7 +15808,7 @@
         <v>4</v>
       </c>
       <c r="S163">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T163">
         <v>3</v>
@@ -15823,19 +15823,19 @@
         <v>6</v>
       </c>
       <c r="X163">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y163">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z163">
         <v>2</v>
       </c>
       <c r="AA163">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB163">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164" spans="1:28">
@@ -15900,7 +15900,7 @@
         <v>6</v>
       </c>
       <c r="U164">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V164">
         <v>5</v>
@@ -15974,7 +15974,7 @@
         <v>6</v>
       </c>
       <c r="Q165">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R165">
         <v>5</v>
@@ -15986,7 +15986,7 @@
         <v>5</v>
       </c>
       <c r="U165">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V165">
         <v>6</v>
@@ -15998,7 +15998,7 @@
         <v>4</v>
       </c>
       <c r="Y165">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z165">
         <v>4</v>
@@ -16030,7 +16030,7 @@
         <v>5</v>
       </c>
       <c r="G166">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H166">
         <v>6</v>
@@ -16039,7 +16039,7 @@
         <v>3</v>
       </c>
       <c r="J166">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K166">
         <v>4</v>
@@ -16060,13 +16060,13 @@
         <v>4</v>
       </c>
       <c r="Q166">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R166">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S166">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T166">
         <v>3</v>
@@ -16110,7 +16110,7 @@
         <v>274</v>
       </c>
       <c r="E167">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F167">
         <v>4</v>
@@ -16119,10 +16119,10 @@
         <v>5</v>
       </c>
       <c r="H167">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I167">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J167">
         <v>5</v>
@@ -16131,7 +16131,7 @@
         <v>5</v>
       </c>
       <c r="L167">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M167">
         <v>4</v>
@@ -16140,7 +16140,7 @@
         <v>3</v>
       </c>
       <c r="O167">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P167">
         <v>5</v>
@@ -16149,10 +16149,10 @@
         <v>7</v>
       </c>
       <c r="R167">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S167">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T167">
         <v>7</v>
@@ -16161,13 +16161,13 @@
         <v>6</v>
       </c>
       <c r="V167">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W167">
         <v>6</v>
       </c>
       <c r="X167">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y167">
         <v>3</v>
@@ -16176,10 +16176,10 @@
         <v>2</v>
       </c>
       <c r="AA167">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB167">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168" spans="1:28">
@@ -16211,7 +16211,7 @@
         <v>3</v>
       </c>
       <c r="J168">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K168">
         <v>6</v>
@@ -16543,7 +16543,7 @@
         <v>5</v>
       </c>
       <c r="F172">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G172">
         <v>5</v>
@@ -16552,7 +16552,7 @@
         <v>5</v>
       </c>
       <c r="I172">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J172">
         <v>5</v>
@@ -16561,55 +16561,55 @@
         <v>6</v>
       </c>
       <c r="L172">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M172">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N172">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O172">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P172">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q172">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R172">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S172">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T172">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U172">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V172">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W172">
         <v>6</v>
       </c>
       <c r="X172">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y172">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z172">
         <v>6</v>
       </c>
       <c r="AA172">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB172">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173" spans="1:28">
@@ -16662,13 +16662,13 @@
         <v>5</v>
       </c>
       <c r="Q173">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R173">
         <v>5</v>
       </c>
       <c r="S173">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T173">
         <v>5</v>
@@ -16677,7 +16677,7 @@
         <v>5</v>
       </c>
       <c r="V173">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W173">
         <v>6</v>
@@ -16689,7 +16689,7 @@
         <v>4</v>
       </c>
       <c r="Z173">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA173">
         <v>4</v>
@@ -16715,7 +16715,7 @@
         <v>4</v>
       </c>
       <c r="F174">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G174">
         <v>4</v>
@@ -16730,22 +16730,22 @@
         <v>4</v>
       </c>
       <c r="K174">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L174">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M174">
         <v>4</v>
       </c>
       <c r="N174">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O174">
         <v>3</v>
       </c>
       <c r="P174">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q174">
         <v>6</v>
@@ -16754,13 +16754,13 @@
         <v>4</v>
       </c>
       <c r="S174">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T174">
         <v>5</v>
       </c>
       <c r="U174">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V174">
         <v>5</v>
@@ -16769,7 +16769,7 @@
         <v>6</v>
       </c>
       <c r="X174">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y174">
         <v>4</v>
@@ -16801,7 +16801,7 @@
         <v>5</v>
       </c>
       <c r="F175">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G175">
         <v>4</v>
@@ -16810,13 +16810,13 @@
         <v>5</v>
       </c>
       <c r="I175">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J175">
         <v>5</v>
       </c>
       <c r="K175">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L175">
         <v>4</v>
@@ -16828,7 +16828,7 @@
         <v>3</v>
       </c>
       <c r="O175">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P175">
         <v>5</v>
@@ -16837,13 +16837,13 @@
         <v>6</v>
       </c>
       <c r="R175">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S175">
         <v>6</v>
       </c>
       <c r="T175">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U175">
         <v>6</v>
@@ -16884,7 +16884,7 @@
         <v>283</v>
       </c>
       <c r="E176">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F176">
         <v>5</v>
@@ -16896,13 +16896,13 @@
         <v>5</v>
       </c>
       <c r="I176">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J176">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K176">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L176">
         <v>6</v>
@@ -16914,13 +16914,13 @@
         <v>3</v>
       </c>
       <c r="O176">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P176">
         <v>5</v>
       </c>
       <c r="Q176">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R176">
         <v>7</v>
@@ -16929,13 +16929,13 @@
         <v>5</v>
       </c>
       <c r="T176">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U176">
         <v>6</v>
       </c>
       <c r="V176">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W176">
         <v>6</v>
@@ -16973,7 +16973,7 @@
         <v>5</v>
       </c>
       <c r="F177">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G177">
         <v>5</v>
@@ -16985,7 +16985,7 @@
         <v>3</v>
       </c>
       <c r="J177">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K177">
         <v>5</v>
@@ -17151,7 +17151,7 @@
         <v>5</v>
       </c>
       <c r="H179">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I179">
         <v>3</v>
@@ -17163,7 +17163,7 @@
         <v>6</v>
       </c>
       <c r="L179">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M179">
         <v>5</v>
@@ -17199,7 +17199,7 @@
         <v>6</v>
       </c>
       <c r="X179">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y179">
         <v>1</v>
@@ -17267,25 +17267,25 @@
         <v>6</v>
       </c>
       <c r="R180">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S180">
         <v>6</v>
       </c>
       <c r="T180">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U180">
         <v>4</v>
       </c>
       <c r="V180">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W180">
         <v>6</v>
       </c>
       <c r="X180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y180">
         <v>3</v>
@@ -17332,7 +17332,7 @@
         <v>4</v>
       </c>
       <c r="K181">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L181">
         <v>4</v>
@@ -17341,13 +17341,13 @@
         <v>4</v>
       </c>
       <c r="N181">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O181">
         <v>4</v>
       </c>
       <c r="P181">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q181">
         <v>6</v>
@@ -17356,13 +17356,13 @@
         <v>5</v>
       </c>
       <c r="S181">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T181">
         <v>5</v>
       </c>
       <c r="U181">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V181">
         <v>4</v>
@@ -17377,10 +17377,10 @@
         <v>4</v>
       </c>
       <c r="Z181">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA181">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB181">
         <v>4</v>
@@ -17403,13 +17403,13 @@
         <v>3</v>
       </c>
       <c r="F182">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G182">
         <v>3</v>
       </c>
       <c r="H182">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I182">
         <v>5</v>
@@ -17418,7 +17418,7 @@
         <v>4</v>
       </c>
       <c r="K182">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L182">
         <v>3</v>
@@ -17439,37 +17439,37 @@
         <v>4</v>
       </c>
       <c r="R182">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S182">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T182">
         <v>5</v>
       </c>
       <c r="U182">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V182">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W182">
         <v>6</v>
       </c>
       <c r="X182">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y182">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z182">
         <v>2</v>
       </c>
       <c r="AA182">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB182">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183" spans="1:28">
@@ -17587,7 +17587,7 @@
         <v>4</v>
       </c>
       <c r="J184">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K184">
         <v>5</v>
@@ -17658,7 +17658,7 @@
         <v>292</v>
       </c>
       <c r="E185">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F185">
         <v>3</v>
@@ -17703,13 +17703,13 @@
         <v>4</v>
       </c>
       <c r="T185">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U185">
         <v>5</v>
       </c>
       <c r="V185">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W185">
         <v>6</v>
@@ -17727,7 +17727,7 @@
         <v>1</v>
       </c>
       <c r="AB185">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:28">
@@ -17919,7 +17919,7 @@
         <v>4</v>
       </c>
       <c r="F188">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G188">
         <v>5</v>
@@ -17958,16 +17958,16 @@
         <v>6</v>
       </c>
       <c r="S188">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T188">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U188">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V188">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W188">
         <v>6</v>
@@ -18044,7 +18044,7 @@
         <v>5</v>
       </c>
       <c r="S189">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T189">
         <v>7</v>
@@ -18151,7 +18151,7 @@
         <v>2</v>
       </c>
       <c r="Z190">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA190">
         <v>2</v>
@@ -18174,10 +18174,10 @@
         <v>298</v>
       </c>
       <c r="E191">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F191">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G191">
         <v>4</v>
@@ -18186,10 +18186,10 @@
         <v>6</v>
       </c>
       <c r="I191">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J191">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K191">
         <v>5</v>
@@ -18198,31 +18198,31 @@
         <v>5</v>
       </c>
       <c r="M191">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N191">
         <v>3</v>
       </c>
       <c r="O191">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P191">
         <v>5</v>
       </c>
       <c r="Q191">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R191">
         <v>4</v>
       </c>
       <c r="S191">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T191">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U191">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V191">
         <v>4</v>
@@ -18231,13 +18231,13 @@
         <v>6</v>
       </c>
       <c r="X191">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y191">
         <v>1</v>
       </c>
       <c r="Z191">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA191">
         <v>1</v>
@@ -18355,7 +18355,7 @@
         <v>4</v>
       </c>
       <c r="H193">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I193">
         <v>4</v>
@@ -18438,7 +18438,7 @@
         <v>4</v>
       </c>
       <c r="G194">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H194">
         <v>4</v>
@@ -18447,25 +18447,25 @@
         <v>4</v>
       </c>
       <c r="J194">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K194">
         <v>5</v>
       </c>
       <c r="L194">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M194">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N194">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O194">
         <v>4</v>
       </c>
       <c r="P194">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q194">
         <v>5</v>
@@ -18536,7 +18536,7 @@
         <v>4</v>
       </c>
       <c r="K195">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L195">
         <v>5</v>
@@ -18554,37 +18554,37 @@
         <v>4</v>
       </c>
       <c r="Q195">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R195">
         <v>4</v>
       </c>
       <c r="S195">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T195">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U195">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V195">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W195">
         <v>6</v>
       </c>
       <c r="X195">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y195">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z195">
         <v>4</v>
       </c>
       <c r="AA195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB195">
         <v>5</v>
@@ -18631,13 +18631,13 @@
         <v>5</v>
       </c>
       <c r="N196">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O196">
         <v>6</v>
       </c>
       <c r="P196">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -18690,10 +18690,10 @@
         <v>304</v>
       </c>
       <c r="E197">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F197">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G197">
         <v>4</v>
@@ -18711,7 +18711,7 @@
         <v>5</v>
       </c>
       <c r="L197">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M197">
         <v>5</v>
@@ -18735,10 +18735,10 @@
         <v>3</v>
       </c>
       <c r="T197">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U197">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V197">
         <v>2</v>
@@ -18747,19 +18747,19 @@
         <v>6</v>
       </c>
       <c r="X197">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y197">
         <v>5</v>
       </c>
       <c r="Z197">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA197">
         <v>5</v>
       </c>
       <c r="AB197">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="198" spans="1:28">
@@ -18827,7 +18827,7 @@
         <v>5</v>
       </c>
       <c r="V198">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W198">
         <v>6</v>
@@ -18898,10 +18898,10 @@
         <v>4</v>
       </c>
       <c r="Q199">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R199">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S199">
         <v>3</v>
@@ -18925,7 +18925,7 @@
         <v>4</v>
       </c>
       <c r="Z199">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA199">
         <v>3</v>
@@ -18996,10 +18996,10 @@
         <v>7</v>
       </c>
       <c r="U200">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V200">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W200">
         <v>6</v>
@@ -19070,7 +19070,7 @@
         <v>5</v>
       </c>
       <c r="Q201">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R201">
         <v>6</v>
@@ -19168,7 +19168,7 @@
         <v>5</v>
       </c>
       <c r="U202">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V202">
         <v>5</v>
@@ -19292,7 +19292,7 @@
         <v>311</v>
       </c>
       <c r="E204">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F204">
         <v>5</v>
@@ -19352,7 +19352,7 @@
         <v>4</v>
       </c>
       <c r="Y204">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z204">
         <v>4</v>
@@ -19361,7 +19361,7 @@
         <v>4</v>
       </c>
       <c r="AB204">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205" spans="1:28">
@@ -19384,7 +19384,7 @@
         <v>5</v>
       </c>
       <c r="G205">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H205">
         <v>5</v>
@@ -19429,7 +19429,7 @@
         <v>5</v>
       </c>
       <c r="V205">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W205">
         <v>6</v>
@@ -19438,7 +19438,7 @@
         <v>3</v>
       </c>
       <c r="Y205">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z205">
         <v>1</v>
@@ -19447,7 +19447,7 @@
         <v>2</v>
       </c>
       <c r="AB205">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206" spans="1:28">
@@ -19470,7 +19470,7 @@
         <v>2</v>
       </c>
       <c r="G206">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H206">
         <v>3</v>
@@ -19506,13 +19506,13 @@
         <v>5</v>
       </c>
       <c r="S206">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T206">
         <v>4</v>
       </c>
       <c r="U206">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V206">
         <v>5</v>
@@ -19616,10 +19616,10 @@
         <v>3</v>
       </c>
       <c r="AA207">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB207">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208" spans="1:28">
@@ -19636,7 +19636,7 @@
         <v>315</v>
       </c>
       <c r="E208">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F208">
         <v>5</v>
@@ -19648,13 +19648,13 @@
         <v>5</v>
       </c>
       <c r="I208">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J208">
         <v>6</v>
       </c>
       <c r="K208">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L208">
         <v>5</v>
@@ -19666,13 +19666,13 @@
         <v>3</v>
       </c>
       <c r="O208">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P208">
         <v>5</v>
       </c>
       <c r="Q208">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R208">
         <v>5</v>
@@ -19693,16 +19693,16 @@
         <v>6</v>
       </c>
       <c r="X208">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y208">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z208">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA208">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB208">
         <v>2</v>
@@ -19728,13 +19728,13 @@
         <v>3</v>
       </c>
       <c r="G209">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H209">
         <v>2</v>
       </c>
       <c r="I209">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J209">
         <v>2</v>
@@ -19752,43 +19752,43 @@
         <v>5</v>
       </c>
       <c r="O209">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P209">
         <v>3</v>
       </c>
       <c r="Q209">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R209">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S209">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T209">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U209">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V209">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W209">
         <v>6</v>
       </c>
       <c r="X209">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y209">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z209">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA209">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB209">
         <v>6</v>
@@ -19817,7 +19817,7 @@
         <v>5</v>
       </c>
       <c r="H210">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I210">
         <v>3</v>
@@ -19835,13 +19835,13 @@
         <v>5</v>
       </c>
       <c r="N210">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O210">
         <v>5</v>
       </c>
       <c r="P210">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q210">
         <v>5</v>
@@ -19992,7 +19992,7 @@
         <v>5</v>
       </c>
       <c r="I212">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J212">
         <v>4</v>
@@ -20010,7 +20010,7 @@
         <v>4</v>
       </c>
       <c r="O212">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P212">
         <v>4</v>
@@ -20022,7 +20022,7 @@
         <v>3</v>
       </c>
       <c r="S212">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T212">
         <v>3</v>
@@ -20037,7 +20037,7 @@
         <v>6</v>
       </c>
       <c r="X212">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y212">
         <v>2</v>
@@ -20049,7 +20049,7 @@
         <v>3</v>
       </c>
       <c r="AB212">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213" spans="1:28">
@@ -20078,13 +20078,13 @@
         <v>4</v>
       </c>
       <c r="I213">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J213">
         <v>4</v>
       </c>
       <c r="K213">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L213">
         <v>3</v>
@@ -20096,40 +20096,40 @@
         <v>6</v>
       </c>
       <c r="O213">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P213">
         <v>2</v>
       </c>
       <c r="Q213">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R213">
         <v>5</v>
       </c>
       <c r="S213">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T213">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U213">
         <v>3</v>
       </c>
       <c r="V213">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W213">
         <v>6</v>
       </c>
       <c r="X213">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y213">
         <v>4</v>
       </c>
       <c r="Z213">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA213">
         <v>4</v>
@@ -20250,10 +20250,10 @@
         <v>5</v>
       </c>
       <c r="I215">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J215">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K215">
         <v>4</v>
@@ -20268,7 +20268,7 @@
         <v>4</v>
       </c>
       <c r="O215">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P215">
         <v>4</v>
@@ -20301,13 +20301,13 @@
         <v>3</v>
       </c>
       <c r="Z215">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA215">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB215">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="216" spans="1:28">
@@ -20345,7 +20345,7 @@
         <v>5</v>
       </c>
       <c r="L216">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M216">
         <v>4</v>
@@ -20360,13 +20360,13 @@
         <v>4</v>
       </c>
       <c r="Q216">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R216">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S216">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T216">
         <v>4</v>
@@ -20393,7 +20393,7 @@
         <v>3</v>
       </c>
       <c r="AB216">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217" spans="1:28">
@@ -20499,7 +20499,7 @@
         <v>5</v>
       </c>
       <c r="F218">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G218">
         <v>6</v>
@@ -20517,10 +20517,10 @@
         <v>5</v>
       </c>
       <c r="L218">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M218">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N218">
         <v>4</v>
@@ -20532,7 +20532,7 @@
         <v>4</v>
       </c>
       <c r="Q218">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R218">
         <v>5</v>
@@ -20562,10 +20562,10 @@
         <v>1</v>
       </c>
       <c r="AA218">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB218">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219" spans="1:28">
@@ -20671,7 +20671,7 @@
         <v>6</v>
       </c>
       <c r="F220">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G220">
         <v>6</v>
@@ -20695,25 +20695,25 @@
         <v>5</v>
       </c>
       <c r="N220">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O220">
         <v>5</v>
       </c>
       <c r="P220">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q220">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R220">
         <v>5</v>
       </c>
       <c r="S220">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T220">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U220">
         <v>6</v>
@@ -20728,7 +20728,7 @@
         <v>2</v>
       </c>
       <c r="Y220">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z220">
         <v>2</v>
@@ -20820,7 +20820,7 @@
         <v>1</v>
       </c>
       <c r="AA221">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB221">
         <v>3</v>
@@ -20846,7 +20846,7 @@
         <v>5</v>
       </c>
       <c r="G222">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H222">
         <v>4</v>
@@ -21155,7 +21155,7 @@
         <v>6</v>
       </c>
       <c r="X225">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y225">
         <v>3</v>
@@ -21164,7 +21164,7 @@
         <v>3</v>
       </c>
       <c r="AA225">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB225">
         <v>3</v>
@@ -21184,10 +21184,10 @@
         <v>333</v>
       </c>
       <c r="E226">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F226">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G226">
         <v>4</v>
@@ -21211,13 +21211,13 @@
         <v>3</v>
       </c>
       <c r="N226">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O226">
         <v>3</v>
       </c>
       <c r="P226">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q226">
         <v>4</v>
@@ -21229,31 +21229,31 @@
         <v>3</v>
       </c>
       <c r="T226">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U226">
         <v>4</v>
       </c>
       <c r="V226">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W226">
         <v>6</v>
       </c>
       <c r="X226">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y226">
         <v>3</v>
       </c>
       <c r="Z226">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA226">
         <v>4</v>
       </c>
       <c r="AB226">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227" spans="1:28">
@@ -21270,10 +21270,10 @@
         <v>334</v>
       </c>
       <c r="E227">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F227">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G227">
         <v>2</v>
@@ -21282,7 +21282,7 @@
         <v>4</v>
       </c>
       <c r="I227">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J227">
         <v>4</v>
@@ -21294,13 +21294,13 @@
         <v>4</v>
       </c>
       <c r="M227">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N227">
         <v>5</v>
       </c>
       <c r="O227">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P227">
         <v>3</v>
@@ -21312,16 +21312,16 @@
         <v>3</v>
       </c>
       <c r="S227">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T227">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U227">
         <v>2</v>
       </c>
       <c r="V227">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W227">
         <v>6</v>
@@ -21336,7 +21336,7 @@
         <v>6</v>
       </c>
       <c r="AA227">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB227">
         <v>6</v>
@@ -21356,7 +21356,7 @@
         <v>335</v>
       </c>
       <c r="E228">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F228">
         <v>5</v>
@@ -21371,16 +21371,16 @@
         <v>4</v>
       </c>
       <c r="J228">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K228">
         <v>4</v>
       </c>
       <c r="L228">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M228">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N228">
         <v>3</v>
@@ -21395,34 +21395,34 @@
         <v>3</v>
       </c>
       <c r="R228">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S228">
         <v>4</v>
       </c>
       <c r="T228">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U228">
         <v>4</v>
       </c>
       <c r="V228">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W228">
         <v>6</v>
       </c>
       <c r="X228">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y228">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z228">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA228">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB228">
         <v>3</v>
@@ -21490,7 +21490,7 @@
         <v>5</v>
       </c>
       <c r="U229">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V229">
         <v>5</v>
@@ -21650,7 +21650,7 @@
         <v>3</v>
       </c>
       <c r="Q231">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R231">
         <v>3</v>
@@ -21674,7 +21674,7 @@
         <v>5</v>
       </c>
       <c r="Y231">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z231">
         <v>5</v>
@@ -21700,10 +21700,10 @@
         <v>298</v>
       </c>
       <c r="E232">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F232">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G232">
         <v>4</v>
@@ -21712,10 +21712,10 @@
         <v>6</v>
       </c>
       <c r="I232">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J232">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K232">
         <v>5</v>
@@ -21724,31 +21724,31 @@
         <v>5</v>
       </c>
       <c r="M232">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N232">
         <v>3</v>
       </c>
       <c r="O232">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P232">
         <v>5</v>
       </c>
       <c r="Q232">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R232">
         <v>4</v>
       </c>
       <c r="S232">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T232">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U232">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V232">
         <v>4</v>
@@ -21757,13 +21757,13 @@
         <v>6</v>
       </c>
       <c r="X232">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y232">
         <v>1</v>
       </c>
       <c r="Z232">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA232">
         <v>1</v>
@@ -21961,7 +21961,7 @@
         <v>3</v>
       </c>
       <c r="F235">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G235">
         <v>4</v>
@@ -21970,10 +21970,10 @@
         <v>3</v>
       </c>
       <c r="I235">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J235">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K235">
         <v>4</v>
@@ -21988,7 +21988,7 @@
         <v>4</v>
       </c>
       <c r="O235">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P235">
         <v>4</v>
@@ -22000,10 +22000,10 @@
         <v>4</v>
       </c>
       <c r="S235">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T235">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U235">
         <v>5</v>
@@ -22015,10 +22015,10 @@
         <v>6</v>
       </c>
       <c r="X235">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y235">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z235">
         <v>6</v>
@@ -22059,16 +22059,16 @@
         <v>3</v>
       </c>
       <c r="J236">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K236">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L236">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M236">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N236">
         <v>3</v>
@@ -22083,7 +22083,7 @@
         <v>2</v>
       </c>
       <c r="R236">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S236">
         <v>4</v>
@@ -22095,7 +22095,7 @@
         <v>3</v>
       </c>
       <c r="V236">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W236">
         <v>6</v>
@@ -22225,7 +22225,7 @@
         <v>5</v>
       </c>
       <c r="H238">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I238">
         <v>3</v>
@@ -22305,19 +22305,19 @@
         <v>4</v>
       </c>
       <c r="F239">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G239">
         <v>3</v>
       </c>
       <c r="H239">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I239">
         <v>4</v>
       </c>
       <c r="J239">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K239">
         <v>5</v>
@@ -22359,19 +22359,19 @@
         <v>6</v>
       </c>
       <c r="X239">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y239">
         <v>2</v>
       </c>
       <c r="Z239">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA239">
         <v>4</v>
       </c>
       <c r="AB239">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="240" spans="1:28">
@@ -22682,7 +22682,7 @@
         <v>4</v>
       </c>
       <c r="Q243">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R243">
         <v>3</v>
@@ -22925,19 +22925,19 @@
         <v>4</v>
       </c>
       <c r="L246">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M246">
         <v>4</v>
       </c>
       <c r="N246">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O246">
         <v>5</v>
       </c>
       <c r="P246">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q246">
         <v>5</v>
@@ -22946,7 +22946,7 @@
         <v>5</v>
       </c>
       <c r="S246">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T246">
         <v>5</v>
@@ -22967,10 +22967,10 @@
         <v>4</v>
       </c>
       <c r="Z246">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA246">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB246">
         <v>5</v>
@@ -23035,13 +23035,13 @@
         <v>5</v>
       </c>
       <c r="T247">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U247">
         <v>4</v>
       </c>
       <c r="V247">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W247">
         <v>6</v>
@@ -23059,7 +23059,7 @@
         <v>3</v>
       </c>
       <c r="AB247">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="248" spans="1:28">
@@ -23076,19 +23076,19 @@
         <v>354</v>
       </c>
       <c r="E248">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F248">
         <v>4</v>
       </c>
       <c r="G248">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H248">
         <v>5</v>
       </c>
       <c r="I248">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J248">
         <v>5</v>
@@ -23106,16 +23106,16 @@
         <v>2</v>
       </c>
       <c r="O248">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P248">
         <v>6</v>
       </c>
       <c r="Q248">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R248">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S248">
         <v>6</v>
@@ -23127,7 +23127,7 @@
         <v>5</v>
       </c>
       <c r="V248">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W248">
         <v>6</v>
@@ -23136,13 +23136,13 @@
         <v>4</v>
       </c>
       <c r="Y248">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z248">
         <v>4</v>
       </c>
       <c r="AA248">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB248">
         <v>4</v>
@@ -23168,13 +23168,13 @@
         <v>4</v>
       </c>
       <c r="G249">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H249">
         <v>4</v>
       </c>
       <c r="I249">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J249">
         <v>4</v>
@@ -23192,7 +23192,7 @@
         <v>4</v>
       </c>
       <c r="O249">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P249">
         <v>4</v>
@@ -23201,7 +23201,7 @@
         <v>5</v>
       </c>
       <c r="R249">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S249">
         <v>7</v>
@@ -23225,10 +23225,10 @@
         <v>2</v>
       </c>
       <c r="Z249">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA249">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB249">
         <v>2</v>
@@ -23263,13 +23263,13 @@
         <v>4</v>
       </c>
       <c r="J250">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K250">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L250">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M250">
         <v>4</v>
@@ -23284,7 +23284,7 @@
         <v>5</v>
       </c>
       <c r="Q250">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R250">
         <v>3</v>
@@ -23293,19 +23293,19 @@
         <v>4</v>
       </c>
       <c r="T250">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U250">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V250">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W250">
         <v>6</v>
       </c>
       <c r="X250">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y250">
         <v>3</v>
@@ -23346,7 +23346,7 @@
         <v>3</v>
       </c>
       <c r="I251">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J251">
         <v>3</v>
@@ -23364,7 +23364,7 @@
         <v>5</v>
       </c>
       <c r="O251">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P251">
         <v>3</v>
@@ -23382,19 +23382,19 @@
         <v>2</v>
       </c>
       <c r="U251">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V251">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W251">
         <v>6</v>
       </c>
       <c r="X251">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y251">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z251">
         <v>4</v>
@@ -23432,7 +23432,7 @@
         <v>4</v>
       </c>
       <c r="I252">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J252">
         <v>5</v>
@@ -23447,28 +23447,28 @@
         <v>4</v>
       </c>
       <c r="N252">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O252">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P252">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q252">
         <v>6</v>
       </c>
       <c r="R252">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S252">
         <v>5</v>
       </c>
       <c r="T252">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U252">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V252">
         <v>6</v>
@@ -23477,7 +23477,7 @@
         <v>6</v>
       </c>
       <c r="X252">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y252">
         <v>2</v>
@@ -23486,7 +23486,7 @@
         <v>2</v>
       </c>
       <c r="AA252">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB252">
         <v>2</v>
@@ -23524,7 +23524,7 @@
         <v>6</v>
       </c>
       <c r="K253">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L253">
         <v>5</v>
@@ -23545,10 +23545,10 @@
         <v>5</v>
       </c>
       <c r="R253">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S253">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T253">
         <v>4</v>
@@ -23557,7 +23557,7 @@
         <v>4</v>
       </c>
       <c r="V253">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W253">
         <v>6</v>
@@ -23572,7 +23572,7 @@
         <v>4</v>
       </c>
       <c r="AA253">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB253">
         <v>3</v>
@@ -23678,7 +23678,7 @@
         <v>361</v>
       </c>
       <c r="E255">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F255">
         <v>6</v>
@@ -23764,7 +23764,7 @@
         <v>362</v>
       </c>
       <c r="E256">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F256">
         <v>6</v>
@@ -23791,13 +23791,13 @@
         <v>5</v>
       </c>
       <c r="N256">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O256">
         <v>5</v>
       </c>
       <c r="P256">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q256">
         <v>2</v>
@@ -23812,7 +23812,7 @@
         <v>4</v>
       </c>
       <c r="U256">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V256">
         <v>4</v>
@@ -23830,7 +23830,7 @@
         <v>4</v>
       </c>
       <c r="AA256">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB256">
         <v>4</v>
@@ -23919,7 +23919,7 @@
         <v>3</v>
       </c>
       <c r="AB257">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="258" spans="1:28">
@@ -23975,7 +23975,7 @@
         <v>3</v>
       </c>
       <c r="R258">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S258">
         <v>4</v>
@@ -24034,7 +24034,7 @@
         <v>3</v>
       </c>
       <c r="I259">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J259">
         <v>3</v>
@@ -24052,7 +24052,7 @@
         <v>4</v>
       </c>
       <c r="O259">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P259">
         <v>4</v>
@@ -24085,7 +24085,7 @@
         <v>4</v>
       </c>
       <c r="Z259">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA259">
         <v>2</v>
@@ -24114,7 +24114,7 @@
         <v>4</v>
       </c>
       <c r="G260">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H260">
         <v>4</v>
@@ -24123,43 +24123,43 @@
         <v>4</v>
       </c>
       <c r="J260">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K260">
         <v>4</v>
       </c>
       <c r="L260">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M260">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N260">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O260">
         <v>4</v>
       </c>
       <c r="P260">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q260">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R260">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S260">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T260">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U260">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V260">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W260">
         <v>6</v>
@@ -24168,13 +24168,13 @@
         <v>3</v>
       </c>
       <c r="Y260">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z260">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA260">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB260">
         <v>2</v>
@@ -24200,16 +24200,16 @@
         <v>5</v>
       </c>
       <c r="G261">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H261">
         <v>5</v>
       </c>
       <c r="I261">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J261">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K261">
         <v>5</v>
@@ -24224,7 +24224,7 @@
         <v>2</v>
       </c>
       <c r="O261">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P261">
         <v>6</v>
@@ -24239,10 +24239,10 @@
         <v>5</v>
       </c>
       <c r="T261">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U261">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V261">
         <v>4</v>
@@ -24340,16 +24340,16 @@
         <v>3</v>
       </c>
       <c r="Y262">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z262">
         <v>3</v>
       </c>
       <c r="AA262">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB262">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="263" spans="1:28">
@@ -24369,10 +24369,10 @@
         <v>4</v>
       </c>
       <c r="F263">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G263">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H263">
         <v>4</v>
@@ -24393,13 +24393,13 @@
         <v>4</v>
       </c>
       <c r="N263">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O263">
         <v>5</v>
       </c>
       <c r="P263">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q263">
         <v>3</v>
@@ -24411,13 +24411,13 @@
         <v>3</v>
       </c>
       <c r="T263">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U263">
         <v>3</v>
       </c>
       <c r="V263">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W263">
         <v>6</v>
@@ -24429,13 +24429,13 @@
         <v>7</v>
       </c>
       <c r="Z263">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA263">
         <v>5</v>
       </c>
       <c r="AB263">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="264" spans="1:28">
@@ -24467,7 +24467,7 @@
         <v>3</v>
       </c>
       <c r="J264">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K264">
         <v>5</v>
@@ -24500,7 +24500,7 @@
         <v>3</v>
       </c>
       <c r="U264">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V264">
         <v>3</v>
@@ -24547,7 +24547,7 @@
         <v>4</v>
       </c>
       <c r="H265">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I265">
         <v>4</v>
@@ -24556,7 +24556,7 @@
         <v>4</v>
       </c>
       <c r="K265">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L265">
         <v>4</v>
@@ -24580,10 +24580,10 @@
         <v>3</v>
       </c>
       <c r="S265">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T265">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U265">
         <v>4</v>
@@ -24598,13 +24598,13 @@
         <v>2</v>
       </c>
       <c r="Y265">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z265">
         <v>2</v>
       </c>
       <c r="AA265">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB265">
         <v>2</v>
@@ -24630,7 +24630,7 @@
         <v>5</v>
       </c>
       <c r="G266">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H266">
         <v>4</v>
@@ -24663,7 +24663,7 @@
         <v>4</v>
       </c>
       <c r="R266">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S266">
         <v>4</v>
@@ -24675,7 +24675,7 @@
         <v>3</v>
       </c>
       <c r="V266">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W266">
         <v>6</v>
@@ -24690,7 +24690,7 @@
         <v>2</v>
       </c>
       <c r="AA266">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB266">
         <v>1</v>
@@ -24891,13 +24891,13 @@
         <v>4</v>
       </c>
       <c r="H269">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I269">
         <v>3</v>
       </c>
       <c r="J269">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K269">
         <v>5</v>
@@ -24918,7 +24918,7 @@
         <v>4</v>
       </c>
       <c r="Q269">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R269">
         <v>3</v>
@@ -24930,10 +24930,10 @@
         <v>3</v>
       </c>
       <c r="U269">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V269">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W269">
         <v>6</v>
@@ -24945,7 +24945,7 @@
         <v>4</v>
       </c>
       <c r="Z269">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA269">
         <v>4</v>
@@ -24968,13 +24968,13 @@
         <v>376</v>
       </c>
       <c r="E270">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F270">
         <v>5</v>
       </c>
       <c r="G270">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H270">
         <v>5</v>
@@ -24986,7 +24986,7 @@
         <v>4</v>
       </c>
       <c r="K270">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L270">
         <v>4</v>
@@ -25004,13 +25004,13 @@
         <v>4</v>
       </c>
       <c r="Q270">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R270">
         <v>4</v>
       </c>
       <c r="S270">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T270">
         <v>5</v>
@@ -25069,7 +25069,7 @@
         <v>3</v>
       </c>
       <c r="J271">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K271">
         <v>5</v>
@@ -25182,7 +25182,7 @@
         <v>4</v>
       </c>
       <c r="S272">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T272">
         <v>4</v>
@@ -25197,7 +25197,7 @@
         <v>6</v>
       </c>
       <c r="X272">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y272">
         <v>3</v>
@@ -25206,10 +25206,10 @@
         <v>3</v>
       </c>
       <c r="AA272">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB272">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="273" spans="1:28">
@@ -25244,7 +25244,7 @@
         <v>5</v>
       </c>
       <c r="K273">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L273">
         <v>5</v>
@@ -25253,13 +25253,13 @@
         <v>5</v>
       </c>
       <c r="N273">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O273">
         <v>5</v>
       </c>
       <c r="P273">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q273">
         <v>4</v>
@@ -25286,7 +25286,7 @@
         <v>4</v>
       </c>
       <c r="Y273">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z273">
         <v>3</v>
@@ -25351,7 +25351,7 @@
         <v>3</v>
       </c>
       <c r="R274">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S274">
         <v>5</v>
@@ -25404,7 +25404,7 @@
         <v>6</v>
       </c>
       <c r="G275">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H275">
         <v>5</v>
@@ -25484,7 +25484,7 @@
         <v>382</v>
       </c>
       <c r="E276">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F276">
         <v>6</v>
@@ -25496,43 +25496,43 @@
         <v>6</v>
       </c>
       <c r="I276">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J276">
         <v>5</v>
       </c>
       <c r="K276">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L276">
         <v>5</v>
       </c>
       <c r="M276">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N276">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O276">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P276">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q276">
         <v>7</v>
       </c>
       <c r="R276">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S276">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T276">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U276">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V276">
         <v>6</v>
@@ -25541,13 +25541,13 @@
         <v>6</v>
       </c>
       <c r="X276">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y276">
         <v>1</v>
       </c>
       <c r="Z276">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA276">
         <v>3</v>
@@ -25745,7 +25745,7 @@
         <v>6</v>
       </c>
       <c r="F279">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G279">
         <v>6</v>
@@ -25754,7 +25754,7 @@
         <v>6</v>
       </c>
       <c r="I279">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J279">
         <v>5</v>
@@ -25769,13 +25769,13 @@
         <v>6</v>
       </c>
       <c r="N279">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O279">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P279">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q279">
         <v>6</v>
@@ -25840,7 +25840,7 @@
         <v>4</v>
       </c>
       <c r="I280">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J280">
         <v>3</v>
@@ -25858,13 +25858,13 @@
         <v>5</v>
       </c>
       <c r="O280">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P280">
         <v>3</v>
       </c>
       <c r="Q280">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R280">
         <v>4</v>
@@ -25876,7 +25876,7 @@
         <v>2</v>
       </c>
       <c r="U280">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V280">
         <v>3</v>
@@ -25885,16 +25885,16 @@
         <v>6</v>
       </c>
       <c r="X280">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y280">
         <v>4</v>
       </c>
       <c r="Z280">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA280">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB280">
         <v>4</v>
@@ -25950,7 +25950,7 @@
         <v>4</v>
       </c>
       <c r="Q281">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R281">
         <v>5</v>
@@ -25959,13 +25959,13 @@
         <v>3</v>
       </c>
       <c r="T281">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U281">
         <v>4</v>
       </c>
       <c r="V281">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W281">
         <v>6</v>
@@ -25974,10 +25974,10 @@
         <v>4</v>
       </c>
       <c r="Y281">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z281">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA281">
         <v>5</v>
@@ -26027,13 +26027,13 @@
         <v>4</v>
       </c>
       <c r="N282">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O282">
         <v>4</v>
       </c>
       <c r="P282">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q282">
         <v>3</v>
@@ -26042,7 +26042,7 @@
         <v>4</v>
       </c>
       <c r="S282">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T282">
         <v>5</v>
@@ -26220,7 +26220,7 @@
         <v>5</v>
       </c>
       <c r="U284">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V284">
         <v>6</v>
@@ -26347,7 +26347,7 @@
         <v>4</v>
       </c>
       <c r="F286">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G286">
         <v>4</v>
@@ -26371,13 +26371,13 @@
         <v>5</v>
       </c>
       <c r="N286">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O286">
         <v>3</v>
       </c>
       <c r="P286">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q286">
         <v>5</v>
@@ -26410,7 +26410,7 @@
         <v>2</v>
       </c>
       <c r="AA286">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB286">
         <v>1</v>
@@ -26433,7 +26433,7 @@
         <v>5</v>
       </c>
       <c r="F287">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G287">
         <v>5</v>
@@ -26451,10 +26451,10 @@
         <v>5</v>
       </c>
       <c r="L287">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M287">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N287">
         <v>4</v>
@@ -26522,13 +26522,13 @@
         <v>3</v>
       </c>
       <c r="G288">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H288">
         <v>4</v>
       </c>
       <c r="I288">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J288">
         <v>5</v>
@@ -26546,7 +26546,7 @@
         <v>4</v>
       </c>
       <c r="O288">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P288">
         <v>4</v>
@@ -26576,7 +26576,7 @@
         <v>2</v>
       </c>
       <c r="Y288">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z288">
         <v>3</v>
@@ -26662,7 +26662,7 @@
         <v>3</v>
       </c>
       <c r="Y289">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z289">
         <v>4</v>
@@ -26688,13 +26688,13 @@
         <v>396</v>
       </c>
       <c r="E290">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F290">
         <v>3</v>
       </c>
       <c r="G290">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H290">
         <v>4</v>
@@ -26709,10 +26709,10 @@
         <v>3</v>
       </c>
       <c r="L290">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M290">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N290">
         <v>3</v>
@@ -26727,7 +26727,7 @@
         <v>5</v>
       </c>
       <c r="R290">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S290">
         <v>5</v>
@@ -26739,16 +26739,16 @@
         <v>5</v>
       </c>
       <c r="V290">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W290">
         <v>6</v>
       </c>
       <c r="X290">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y290">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z290">
         <v>2</v>
@@ -26774,13 +26774,13 @@
         <v>397</v>
       </c>
       <c r="E291">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F291">
         <v>5</v>
       </c>
       <c r="G291">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H291">
         <v>5</v>
@@ -26801,22 +26801,22 @@
         <v>5</v>
       </c>
       <c r="N291">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O291">
         <v>4</v>
       </c>
       <c r="P291">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q291">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R291">
         <v>6</v>
       </c>
       <c r="S291">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T291">
         <v>6</v>
@@ -26834,10 +26834,10 @@
         <v>3</v>
       </c>
       <c r="Y291">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z291">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA291">
         <v>2</v>
@@ -26967,7 +26967,7 @@
         <v>6</v>
       </c>
       <c r="L293">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M293">
         <v>5</v>
@@ -27418,7 +27418,7 @@
         <v>4</v>
       </c>
       <c r="S298">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T298">
         <v>4</v>
@@ -27436,7 +27436,7 @@
         <v>2</v>
       </c>
       <c r="Y298">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z298">
         <v>4</v>
@@ -27462,7 +27462,7 @@
         <v>405</v>
       </c>
       <c r="E299">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F299">
         <v>5</v>
@@ -27471,7 +27471,7 @@
         <v>5</v>
       </c>
       <c r="H299">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I299">
         <v>3</v>
@@ -27486,7 +27486,7 @@
         <v>5</v>
       </c>
       <c r="M299">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N299">
         <v>3</v>
@@ -27498,13 +27498,13 @@
         <v>5</v>
       </c>
       <c r="Q299">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R299">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S299">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T299">
         <v>6</v>
@@ -27519,7 +27519,7 @@
         <v>6</v>
       </c>
       <c r="X299">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y299">
         <v>3</v>
@@ -27531,7 +27531,7 @@
         <v>4</v>
       </c>
       <c r="AB299">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300" spans="1:28">
@@ -27548,13 +27548,13 @@
         <v>406</v>
       </c>
       <c r="E300">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F300">
         <v>4</v>
       </c>
       <c r="G300">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H300">
         <v>4</v>
@@ -27563,7 +27563,7 @@
         <v>3</v>
       </c>
       <c r="J300">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K300">
         <v>5</v>
@@ -27572,7 +27572,7 @@
         <v>5</v>
       </c>
       <c r="M300">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N300">
         <v>4</v>
@@ -27599,7 +27599,7 @@
         <v>4</v>
       </c>
       <c r="V300">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W300">
         <v>6</v>
@@ -27637,7 +27637,7 @@
         <v>3</v>
       </c>
       <c r="F301">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G301">
         <v>4</v>
@@ -27649,7 +27649,7 @@
         <v>4</v>
       </c>
       <c r="J301">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K301">
         <v>3</v>
@@ -27673,7 +27673,7 @@
         <v>4</v>
       </c>
       <c r="R301">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S301">
         <v>6</v>
@@ -27685,16 +27685,16 @@
         <v>5</v>
       </c>
       <c r="V301">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W301">
         <v>6</v>
       </c>
       <c r="X301">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y301">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z301">
         <v>2</v>
@@ -27703,7 +27703,7 @@
         <v>3</v>
       </c>
       <c r="AB301">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302" spans="1:28">
@@ -27744,7 +27744,7 @@
         <v>6</v>
       </c>
       <c r="M302">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N302">
         <v>4</v>
@@ -27809,7 +27809,7 @@
         <v>6</v>
       </c>
       <c r="F303">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G303">
         <v>6</v>
@@ -27821,7 +27821,7 @@
         <v>2</v>
       </c>
       <c r="J303">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K303">
         <v>5</v>
@@ -27842,19 +27842,19 @@
         <v>5</v>
       </c>
       <c r="Q303">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R303">
         <v>6</v>
       </c>
       <c r="S303">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T303">
         <v>6</v>
       </c>
       <c r="U303">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V303">
         <v>5</v>
@@ -27869,13 +27869,13 @@
         <v>2</v>
       </c>
       <c r="Z303">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA303">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB303">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304" spans="1:28">
@@ -27892,25 +27892,25 @@
         <v>410</v>
       </c>
       <c r="E304">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F304">
         <v>2</v>
       </c>
       <c r="G304">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H304">
         <v>3</v>
       </c>
       <c r="I304">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J304">
         <v>2</v>
       </c>
       <c r="K304">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L304">
         <v>4</v>
@@ -27922,7 +27922,7 @@
         <v>5</v>
       </c>
       <c r="O304">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P304">
         <v>3</v>
@@ -27934,7 +27934,7 @@
         <v>4</v>
       </c>
       <c r="S304">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T304">
         <v>4</v>
@@ -27952,16 +27952,16 @@
         <v>3</v>
       </c>
       <c r="Y304">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z304">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA304">
         <v>3</v>
       </c>
       <c r="AB304">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305" spans="1:28">
@@ -27993,7 +27993,7 @@
         <v>4</v>
       </c>
       <c r="J305">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K305">
         <v>4</v>
@@ -28047,7 +28047,7 @@
         <v>2</v>
       </c>
       <c r="AB305">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="306" spans="1:28">
@@ -28076,7 +28076,7 @@
         <v>5</v>
       </c>
       <c r="I306">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J306">
         <v>4</v>
@@ -28094,7 +28094,7 @@
         <v>4</v>
       </c>
       <c r="O306">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P306">
         <v>4</v>
@@ -28103,7 +28103,7 @@
         <v>6</v>
       </c>
       <c r="R306">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S306">
         <v>7</v>
@@ -28115,7 +28115,7 @@
         <v>6</v>
       </c>
       <c r="V306">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W306">
         <v>6</v>
@@ -28192,7 +28192,7 @@
         <v>6</v>
       </c>
       <c r="S307">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T307">
         <v>4</v>
@@ -28210,7 +28210,7 @@
         <v>1</v>
       </c>
       <c r="Y307">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z307">
         <v>1</v>
@@ -28242,7 +28242,7 @@
         <v>5</v>
       </c>
       <c r="G308">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H308">
         <v>5</v>
@@ -28254,13 +28254,13 @@
         <v>5</v>
       </c>
       <c r="K308">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L308">
         <v>4</v>
       </c>
       <c r="M308">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N308">
         <v>4</v>
@@ -28272,19 +28272,19 @@
         <v>4</v>
       </c>
       <c r="Q308">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R308">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S308">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T308">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U308">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V308">
         <v>6</v>
@@ -28293,19 +28293,19 @@
         <v>6</v>
       </c>
       <c r="X308">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y308">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z308">
         <v>2</v>
       </c>
       <c r="AA308">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB308">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="309" spans="1:28">
@@ -28580,19 +28580,19 @@
         <v>418</v>
       </c>
       <c r="E312">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F312">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G312">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H312">
         <v>6</v>
       </c>
       <c r="I312">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J312">
         <v>6</v>
@@ -28607,13 +28607,13 @@
         <v>6</v>
       </c>
       <c r="N312">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O312">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P312">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q312">
         <v>7</v>
@@ -28637,7 +28637,7 @@
         <v>6</v>
       </c>
       <c r="X312">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y312">
         <v>1</v>
@@ -28646,10 +28646,10 @@
         <v>1</v>
       </c>
       <c r="AA312">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB312">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313" spans="1:28">
@@ -28761,7 +28761,7 @@
         <v>4</v>
       </c>
       <c r="H314">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I314">
         <v>5</v>
@@ -28788,7 +28788,7 @@
         <v>2</v>
       </c>
       <c r="Q314">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R314">
         <v>5</v>
@@ -28818,7 +28818,7 @@
         <v>4</v>
       </c>
       <c r="AA314">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB314">
         <v>4</v>
@@ -28844,7 +28844,7 @@
         <v>5</v>
       </c>
       <c r="G315">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H315">
         <v>4</v>
@@ -28877,10 +28877,10 @@
         <v>5</v>
       </c>
       <c r="R315">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S315">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T315">
         <v>4</v>
@@ -28907,7 +28907,7 @@
         <v>4</v>
       </c>
       <c r="AB315">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="316" spans="1:28">
@@ -28942,7 +28942,7 @@
         <v>5</v>
       </c>
       <c r="K316">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L316">
         <v>6</v>
@@ -29159,7 +29159,7 @@
         <v>6</v>
       </c>
       <c r="Z318">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA318">
         <v>4</v>
@@ -29182,7 +29182,7 @@
         <v>425</v>
       </c>
       <c r="E319">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F319">
         <v>4</v>
@@ -29363,7 +29363,7 @@
         <v>5</v>
       </c>
       <c r="H321">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I321">
         <v>3</v>
@@ -29399,7 +29399,7 @@
         <v>4</v>
       </c>
       <c r="T321">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U321">
         <v>4</v>
@@ -29414,16 +29414,16 @@
         <v>1</v>
       </c>
       <c r="Y321">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z321">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA321">
         <v>2</v>
       </c>
       <c r="AB321">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="322" spans="1:28">
@@ -29440,7 +29440,7 @@
         <v>428</v>
       </c>
       <c r="E322">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F322">
         <v>5</v>
@@ -29476,22 +29476,22 @@
         <v>4</v>
       </c>
       <c r="Q322">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R322">
         <v>7</v>
       </c>
       <c r="S322">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T322">
         <v>7</v>
       </c>
       <c r="U322">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V322">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W322">
         <v>6</v>
@@ -29526,10 +29526,10 @@
         <v>429</v>
       </c>
       <c r="E323">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F323">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G323">
         <v>4</v>
@@ -29541,7 +29541,7 @@
         <v>4</v>
       </c>
       <c r="J323">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K323">
         <v>4</v>
@@ -29639,13 +29639,13 @@
         <v>6</v>
       </c>
       <c r="N324">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O324">
         <v>5</v>
       </c>
       <c r="P324">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q324">
         <v>5</v>
@@ -29710,13 +29710,13 @@
         <v>4</v>
       </c>
       <c r="I325">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J325">
         <v>3</v>
       </c>
       <c r="K325">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L325">
         <v>4</v>
@@ -29728,28 +29728,28 @@
         <v>4</v>
       </c>
       <c r="O325">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P325">
         <v>4</v>
       </c>
       <c r="Q325">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R325">
         <v>3</v>
       </c>
       <c r="S325">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T325">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U325">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V325">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W325">
         <v>6</v>
@@ -29758,7 +29758,7 @@
         <v>4</v>
       </c>
       <c r="Y325">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z325">
         <v>2</v>
@@ -29767,7 +29767,7 @@
         <v>3</v>
       </c>
       <c r="AB325">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="326" spans="1:28">
@@ -29790,7 +29790,7 @@
         <v>5</v>
       </c>
       <c r="G326">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H326">
         <v>4</v>
@@ -29805,7 +29805,7 @@
         <v>3</v>
       </c>
       <c r="L326">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M326">
         <v>4</v>
@@ -29820,19 +29820,19 @@
         <v>5</v>
       </c>
       <c r="Q326">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R326">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S326">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T326">
         <v>3</v>
       </c>
       <c r="U326">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V326">
         <v>2</v>
@@ -29844,10 +29844,10 @@
         <v>6</v>
       </c>
       <c r="Y326">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z326">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA326">
         <v>3</v>
@@ -29983,13 +29983,13 @@
         <v>6</v>
       </c>
       <c r="N328">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O328">
         <v>6</v>
       </c>
       <c r="P328">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q328">
         <v>6</v>
@@ -30069,13 +30069,13 @@
         <v>5</v>
       </c>
       <c r="N329">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O329">
         <v>5</v>
       </c>
       <c r="P329">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q329">
         <v>5</v>
@@ -30220,7 +30220,7 @@
         <v>3</v>
       </c>
       <c r="G331">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H331">
         <v>3</v>
@@ -30232,7 +30232,7 @@
         <v>3</v>
       </c>
       <c r="K331">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L331">
         <v>3</v>
@@ -30256,7 +30256,7 @@
         <v>3</v>
       </c>
       <c r="S331">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T331">
         <v>5</v>
@@ -30271,7 +30271,7 @@
         <v>6</v>
       </c>
       <c r="X331">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y331">
         <v>2</v>
@@ -30283,7 +30283,7 @@
         <v>3</v>
       </c>
       <c r="AB331">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332" spans="1:28">
@@ -30303,13 +30303,13 @@
         <v>3</v>
       </c>
       <c r="F332">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G332">
         <v>4</v>
       </c>
       <c r="H332">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I332">
         <v>5</v>
@@ -30336,10 +30336,10 @@
         <v>4</v>
       </c>
       <c r="Q332">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R332">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S332">
         <v>7</v>
@@ -30348,16 +30348,16 @@
         <v>7</v>
       </c>
       <c r="U332">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V332">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W332">
         <v>6</v>
       </c>
       <c r="X332">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y332">
         <v>2</v>
@@ -30366,7 +30366,7 @@
         <v>2</v>
       </c>
       <c r="AA332">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB332">
         <v>2</v>
@@ -30422,7 +30422,7 @@
         <v>5</v>
       </c>
       <c r="Q333">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R333">
         <v>5</v>
@@ -30478,7 +30478,7 @@
         <v>5</v>
       </c>
       <c r="G334">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H334">
         <v>6</v>
@@ -30689,7 +30689,7 @@
         <v>4</v>
       </c>
       <c r="T336">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U336">
         <v>5</v>
@@ -30710,7 +30710,7 @@
         <v>2</v>
       </c>
       <c r="AA336">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB336">
         <v>2</v>
@@ -30754,7 +30754,7 @@
         <v>6</v>
       </c>
       <c r="M337">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N337">
         <v>3</v>
@@ -30778,7 +30778,7 @@
         <v>5</v>
       </c>
       <c r="U337">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V337">
         <v>6</v>
@@ -30819,7 +30819,7 @@
         <v>5</v>
       </c>
       <c r="F338">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G338">
         <v>5</v>
@@ -30828,7 +30828,7 @@
         <v>4</v>
       </c>
       <c r="I338">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J338">
         <v>5</v>
@@ -30846,7 +30846,7 @@
         <v>3</v>
       </c>
       <c r="O338">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P338">
         <v>5</v>
@@ -30861,7 +30861,7 @@
         <v>6</v>
       </c>
       <c r="T338">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U338">
         <v>6</v>
@@ -30905,7 +30905,7 @@
         <v>4</v>
       </c>
       <c r="F339">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G339">
         <v>5</v>
@@ -30914,13 +30914,13 @@
         <v>5</v>
       </c>
       <c r="I339">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J339">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K339">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L339">
         <v>5</v>
@@ -30932,7 +30932,7 @@
         <v>2</v>
       </c>
       <c r="O339">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P339">
         <v>6</v>
@@ -30941,7 +30941,7 @@
         <v>6</v>
       </c>
       <c r="R339">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S339">
         <v>6</v>
@@ -30991,7 +30991,7 @@
         <v>5</v>
       </c>
       <c r="F340">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G340">
         <v>6</v>
@@ -31012,7 +31012,7 @@
         <v>5</v>
       </c>
       <c r="M340">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N340">
         <v>3</v>
@@ -31024,7 +31024,7 @@
         <v>5</v>
       </c>
       <c r="Q340">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R340">
         <v>6</v>
@@ -31113,7 +31113,7 @@
         <v>4</v>
       </c>
       <c r="R341">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S341">
         <v>5</v>
@@ -31131,7 +31131,7 @@
         <v>6</v>
       </c>
       <c r="X341">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y341">
         <v>3</v>
@@ -31140,10 +31140,10 @@
         <v>2</v>
       </c>
       <c r="AA341">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB341">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="342" spans="1:28">
@@ -31169,7 +31169,7 @@
         <v>5</v>
       </c>
       <c r="H342">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I342">
         <v>3</v>
@@ -31184,7 +31184,7 @@
         <v>5</v>
       </c>
       <c r="M342">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N342">
         <v>4</v>
@@ -31199,13 +31199,13 @@
         <v>6</v>
       </c>
       <c r="R342">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S342">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T342">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U342">
         <v>7</v>
@@ -31217,7 +31217,7 @@
         <v>6</v>
       </c>
       <c r="X342">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y342">
         <v>2</v>
@@ -31374,7 +31374,7 @@
         <v>5</v>
       </c>
       <c r="S344">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T344">
         <v>6</v>
@@ -31433,10 +31433,10 @@
         <v>3</v>
       </c>
       <c r="J345">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K345">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L345">
         <v>4</v>
@@ -31463,7 +31463,7 @@
         <v>6</v>
       </c>
       <c r="T345">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U345">
         <v>7</v>
@@ -31478,7 +31478,7 @@
         <v>1</v>
       </c>
       <c r="Y345">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z345">
         <v>3</v>
@@ -31504,7 +31504,7 @@
         <v>452</v>
       </c>
       <c r="E346">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F346">
         <v>5</v>
@@ -31525,7 +31525,7 @@
         <v>4</v>
       </c>
       <c r="L346">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M346">
         <v>3</v>
@@ -31691,7 +31691,7 @@
         <v>4</v>
       </c>
       <c r="J348">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K348">
         <v>4</v>
@@ -31736,7 +31736,7 @@
         <v>3</v>
       </c>
       <c r="Y348">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z348">
         <v>1</v>
@@ -31745,7 +31745,7 @@
         <v>2</v>
       </c>
       <c r="AB348">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="349" spans="1:28">
@@ -31768,10 +31768,10 @@
         <v>3</v>
       </c>
       <c r="G349">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H349">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I349">
         <v>3</v>
@@ -31813,7 +31813,7 @@
         <v>5</v>
       </c>
       <c r="V349">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W349">
         <v>6</v>
@@ -31884,13 +31884,13 @@
         <v>3</v>
       </c>
       <c r="Q350">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R350">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S350">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T350">
         <v>4</v>
@@ -31905,16 +31905,16 @@
         <v>6</v>
       </c>
       <c r="X350">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y350">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z350">
         <v>4</v>
       </c>
       <c r="AA350">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB350">
         <v>5</v>
@@ -31943,7 +31943,7 @@
         <v>3</v>
       </c>
       <c r="H351">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I351">
         <v>4</v>
@@ -31994,7 +31994,7 @@
         <v>3</v>
       </c>
       <c r="Y351">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z351">
         <v>2</v>
@@ -32023,7 +32023,7 @@
         <v>4</v>
       </c>
       <c r="F352">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G352">
         <v>4</v>
@@ -32035,7 +32035,7 @@
         <v>5</v>
       </c>
       <c r="J352">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K352">
         <v>4</v>
@@ -32044,7 +32044,7 @@
         <v>3</v>
       </c>
       <c r="M352">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N352">
         <v>4</v>
@@ -32056,7 +32056,7 @@
         <v>4</v>
       </c>
       <c r="Q352">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R352">
         <v>6</v>
@@ -32083,13 +32083,13 @@
         <v>4</v>
       </c>
       <c r="Z352">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA352">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB352">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="353" spans="1:28">
@@ -32121,7 +32121,7 @@
         <v>3</v>
       </c>
       <c r="J353">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K353">
         <v>6</v>
@@ -32249,7 +32249,7 @@
         <v>6</v>
       </c>
       <c r="X354">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y354">
         <v>4</v>
@@ -32320,13 +32320,13 @@
         <v>5</v>
       </c>
       <c r="S355">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T355">
         <v>6</v>
       </c>
       <c r="U355">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V355">
         <v>6</v>
@@ -32338,16 +32338,16 @@
         <v>2</v>
       </c>
       <c r="Y355">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z355">
         <v>3</v>
       </c>
       <c r="AA355">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB355">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356" spans="1:28">
@@ -32412,7 +32412,7 @@
         <v>5</v>
       </c>
       <c r="U356">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V356">
         <v>6</v>
@@ -32450,16 +32450,16 @@
         <v>462</v>
       </c>
       <c r="E357">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F357">
         <v>5</v>
       </c>
       <c r="G357">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H357">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I357">
         <v>2</v>
@@ -32468,22 +32468,22 @@
         <v>5</v>
       </c>
       <c r="K357">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L357">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M357">
         <v>5</v>
       </c>
       <c r="N357">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O357">
         <v>6</v>
       </c>
       <c r="P357">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q357">
         <v>6</v>
@@ -32575,19 +32575,19 @@
         <v>5</v>
       </c>
       <c r="R358">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S358">
         <v>6</v>
       </c>
       <c r="T358">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U358">
         <v>6</v>
       </c>
       <c r="V358">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W358">
         <v>6</v>
@@ -32625,7 +32625,7 @@
         <v>6</v>
       </c>
       <c r="F359">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G359">
         <v>6</v>
@@ -32646,7 +32646,7 @@
         <v>7</v>
       </c>
       <c r="M359">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N359">
         <v>2</v>
@@ -32682,13 +32682,13 @@
         <v>2</v>
       </c>
       <c r="Y359">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z359">
         <v>3</v>
       </c>
       <c r="AA359">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB359">
         <v>2</v>
@@ -32723,7 +32723,7 @@
         <v>2</v>
       </c>
       <c r="J360">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K360">
         <v>6</v>
@@ -32753,7 +32753,7 @@
         <v>5</v>
       </c>
       <c r="T360">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U360">
         <v>5</v>
@@ -32768,7 +32768,7 @@
         <v>2</v>
       </c>
       <c r="Y360">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z360">
         <v>2</v>
@@ -32777,7 +32777,7 @@
         <v>2</v>
       </c>
       <c r="AB360">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="361" spans="1:28">
@@ -32812,10 +32812,10 @@
         <v>6</v>
       </c>
       <c r="K361">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L361">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M361">
         <v>6</v>
@@ -32830,7 +32830,7 @@
         <v>6</v>
       </c>
       <c r="Q361">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R361">
         <v>5</v>
@@ -32845,13 +32845,13 @@
         <v>5</v>
       </c>
       <c r="V361">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W361">
         <v>6</v>
       </c>
       <c r="X361">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y361">
         <v>2</v>
@@ -32940,7 +32940,7 @@
         <v>2</v>
       </c>
       <c r="Y362">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z362">
         <v>2</v>
@@ -32990,16 +32990,16 @@
         <v>5</v>
       </c>
       <c r="M363">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N363">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O363">
         <v>5</v>
       </c>
       <c r="P363">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q363">
         <v>4</v>
@@ -33008,10 +33008,10 @@
         <v>4</v>
       </c>
       <c r="S363">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T363">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U363">
         <v>4</v>
@@ -33138,7 +33138,7 @@
         <v>470</v>
       </c>
       <c r="E365">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F365">
         <v>6</v>
@@ -33156,13 +33156,13 @@
         <v>5</v>
       </c>
       <c r="K365">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L365">
         <v>5</v>
       </c>
       <c r="M365">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N365">
         <v>3</v>
@@ -33183,10 +33183,10 @@
         <v>6</v>
       </c>
       <c r="T365">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U365">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V365">
         <v>4</v>
@@ -33195,16 +33195,16 @@
         <v>6</v>
       </c>
       <c r="X365">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y365">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z365">
         <v>5</v>
       </c>
       <c r="AA365">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB365">
         <v>3</v>
@@ -33242,7 +33242,7 @@
         <v>5</v>
       </c>
       <c r="K366">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L366">
         <v>6</v>
@@ -33266,7 +33266,7 @@
         <v>6</v>
       </c>
       <c r="S366">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T366">
         <v>5</v>
@@ -33275,7 +33275,7 @@
         <v>6</v>
       </c>
       <c r="V366">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W366">
         <v>6</v>
@@ -33352,16 +33352,16 @@
         <v>5</v>
       </c>
       <c r="S367">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T367">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U367">
         <v>5</v>
       </c>
       <c r="V367">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W367">
         <v>6</v>
@@ -33373,7 +33373,7 @@
         <v>3</v>
       </c>
       <c r="Z367">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA367">
         <v>3</v>
@@ -33396,7 +33396,7 @@
         <v>473</v>
       </c>
       <c r="E368">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F368">
         <v>4</v>
@@ -33432,13 +33432,13 @@
         <v>5</v>
       </c>
       <c r="Q368">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R368">
         <v>7</v>
       </c>
       <c r="S368">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T368">
         <v>7</v>
@@ -33447,7 +33447,7 @@
         <v>5</v>
       </c>
       <c r="V368">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W368">
         <v>6</v>
@@ -33518,7 +33518,7 @@
         <v>5</v>
       </c>
       <c r="Q369">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R369">
         <v>3</v>
@@ -33545,7 +33545,7 @@
         <v>4</v>
       </c>
       <c r="Z369">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA369">
         <v>4</v>
@@ -33604,7 +33604,7 @@
         <v>5</v>
       </c>
       <c r="Q370">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R370">
         <v>7</v>
@@ -33616,7 +33616,7 @@
         <v>7</v>
       </c>
       <c r="U370">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V370">
         <v>7</v>
@@ -33625,7 +33625,7 @@
         <v>6</v>
       </c>
       <c r="X370">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y370">
         <v>3</v>
@@ -33634,10 +33634,10 @@
         <v>1</v>
       </c>
       <c r="AA370">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB370">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371" spans="1:28">
@@ -33660,7 +33660,7 @@
         <v>6</v>
       </c>
       <c r="G371">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H371">
         <v>6</v>
@@ -33690,7 +33690,7 @@
         <v>6</v>
       </c>
       <c r="Q371">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R371">
         <v>3</v>
@@ -33699,7 +33699,7 @@
         <v>5</v>
       </c>
       <c r="T371">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U371">
         <v>3</v>
@@ -33832,7 +33832,7 @@
         <v>5</v>
       </c>
       <c r="G373">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H373">
         <v>5</v>
@@ -33868,34 +33868,34 @@
         <v>5</v>
       </c>
       <c r="S373">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T373">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U373">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V373">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W373">
         <v>6</v>
       </c>
       <c r="X373">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y373">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z373">
         <v>2</v>
       </c>
       <c r="AA373">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB373">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="374" spans="1:28">
@@ -33921,13 +33921,13 @@
         <v>6</v>
       </c>
       <c r="H374">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I374">
         <v>2</v>
       </c>
       <c r="J374">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K374">
         <v>6</v>
@@ -34102,7 +34102,7 @@
         <v>4</v>
       </c>
       <c r="K376">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L376">
         <v>4</v>
@@ -34147,7 +34147,7 @@
         <v>2</v>
       </c>
       <c r="Z376">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA376">
         <v>3</v>
